--- a/data/lng_2025_price.xlsx
+++ b/data/lng_2025_price.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F192"/>
+  <dimension ref="A1:F202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4281,7 +4281,207 @@
         <v>3.413000106811523</v>
       </c>
       <c r="F192" t="n">
-        <v>259354</v>
+        <v>217261</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="n">
+        <v>45936</v>
+      </c>
+      <c r="B193" t="n">
+        <v>3.357000112533569</v>
+      </c>
+      <c r="C193" t="n">
+        <v>3.484999895095825</v>
+      </c>
+      <c r="D193" t="n">
+        <v>3.296000003814697</v>
+      </c>
+      <c r="E193" t="n">
+        <v>3.299999952316284</v>
+      </c>
+      <c r="F193" t="n">
+        <v>165229</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="n">
+        <v>45937</v>
+      </c>
+      <c r="B194" t="n">
+        <v>3.497999906539917</v>
+      </c>
+      <c r="C194" t="n">
+        <v>3.523999929428101</v>
+      </c>
+      <c r="D194" t="n">
+        <v>3.355000019073486</v>
+      </c>
+      <c r="E194" t="n">
+        <v>3.398000001907349</v>
+      </c>
+      <c r="F194" t="n">
+        <v>230258</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="n">
+        <v>45938</v>
+      </c>
+      <c r="B195" t="n">
+        <v>3.33299994468689</v>
+      </c>
+      <c r="C195" t="n">
+        <v>3.549999952316284</v>
+      </c>
+      <c r="D195" t="n">
+        <v>3.315999984741211</v>
+      </c>
+      <c r="E195" t="n">
+        <v>3.523999929428101</v>
+      </c>
+      <c r="F195" t="n">
+        <v>242687</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="n">
+        <v>45939</v>
+      </c>
+      <c r="B196" t="n">
+        <v>3.269000053405762</v>
+      </c>
+      <c r="C196" t="n">
+        <v>3.392999887466431</v>
+      </c>
+      <c r="D196" t="n">
+        <v>3.234999895095825</v>
+      </c>
+      <c r="E196" t="n">
+        <v>3.335999965667725</v>
+      </c>
+      <c r="F196" t="n">
+        <v>198680</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="n">
+        <v>45940</v>
+      </c>
+      <c r="B197" t="n">
+        <v>3.105999946594238</v>
+      </c>
+      <c r="C197" t="n">
+        <v>3.253000020980835</v>
+      </c>
+      <c r="D197" t="n">
+        <v>3.08899998664856</v>
+      </c>
+      <c r="E197" t="n">
+        <v>3.239000082015991</v>
+      </c>
+      <c r="F197" t="n">
+        <v>195346</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="n">
+        <v>45943</v>
+      </c>
+      <c r="B198" t="n">
+        <v>3.118000030517578</v>
+      </c>
+      <c r="C198" t="n">
+        <v>3.138000011444092</v>
+      </c>
+      <c r="D198" t="n">
+        <v>3.029000043869019</v>
+      </c>
+      <c r="E198" t="n">
+        <v>3.099999904632568</v>
+      </c>
+      <c r="F198" t="n">
+        <v>195346</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="n">
+        <v>45944</v>
+      </c>
+      <c r="B199" t="n">
+        <v>3.028000116348267</v>
+      </c>
+      <c r="C199" t="n">
+        <v>3.105999946594238</v>
+      </c>
+      <c r="D199" t="n">
+        <v>3.003999948501587</v>
+      </c>
+      <c r="E199" t="n">
+        <v>3.102999925613403</v>
+      </c>
+      <c r="F199" t="n">
+        <v>150478</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="n">
+        <v>45945</v>
+      </c>
+      <c r="B200" t="n">
+        <v>3.016000032424927</v>
+      </c>
+      <c r="C200" t="n">
+        <v>3.040999889373779</v>
+      </c>
+      <c r="D200" t="n">
+        <v>2.96399998664856</v>
+      </c>
+      <c r="E200" t="n">
+        <v>3.029000043869019</v>
+      </c>
+      <c r="F200" t="n">
+        <v>149150</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="n">
+        <v>45946</v>
+      </c>
+      <c r="B201" t="n">
+        <v>2.937999963760376</v>
+      </c>
+      <c r="C201" t="n">
+        <v>3.066999912261963</v>
+      </c>
+      <c r="D201" t="n">
+        <v>2.921999931335449</v>
+      </c>
+      <c r="E201" t="n">
+        <v>3.03600001335144</v>
+      </c>
+      <c r="F201" t="n">
+        <v>161360</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="n">
+        <v>45947</v>
+      </c>
+      <c r="B202" t="n">
+        <v>3.007999897003174</v>
+      </c>
+      <c r="C202" t="n">
+        <v>3.023999929428101</v>
+      </c>
+      <c r="D202" t="n">
+        <v>2.892999887466431</v>
+      </c>
+      <c r="E202" t="n">
+        <v>2.926000118255615</v>
+      </c>
+      <c r="F202" t="n">
+        <v>161360</v>
       </c>
     </row>
   </sheetData>

--- a/data/lng_2025_price.xlsx
+++ b/data/lng_2025_price.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F202"/>
+  <dimension ref="A1:F207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4481,7 +4481,107 @@
         <v>2.926000118255615</v>
       </c>
       <c r="F202" t="n">
-        <v>161360</v>
+        <v>128236</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="n">
+        <v>45950</v>
+      </c>
+      <c r="B203" t="n">
+        <v>3.397000074386597</v>
+      </c>
+      <c r="C203" t="n">
+        <v>3.430000066757202</v>
+      </c>
+      <c r="D203" t="n">
+        <v>3.135999917984009</v>
+      </c>
+      <c r="E203" t="n">
+        <v>3.160000085830688</v>
+      </c>
+      <c r="F203" t="n">
+        <v>266597</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="n">
+        <v>45951</v>
+      </c>
+      <c r="B204" t="n">
+        <v>3.473999977111816</v>
+      </c>
+      <c r="C204" t="n">
+        <v>3.503999948501587</v>
+      </c>
+      <c r="D204" t="n">
+        <v>3.357000112533569</v>
+      </c>
+      <c r="E204" t="n">
+        <v>3.421000003814697</v>
+      </c>
+      <c r="F204" t="n">
+        <v>197775</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="n">
+        <v>45952</v>
+      </c>
+      <c r="B205" t="n">
+        <v>3.450000047683716</v>
+      </c>
+      <c r="C205" t="n">
+        <v>3.572000026702881</v>
+      </c>
+      <c r="D205" t="n">
+        <v>3.385999917984009</v>
+      </c>
+      <c r="E205" t="n">
+        <v>3.486999988555908</v>
+      </c>
+      <c r="F205" t="n">
+        <v>202361</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="n">
+        <v>45953</v>
+      </c>
+      <c r="B206" t="n">
+        <v>3.344000101089478</v>
+      </c>
+      <c r="C206" t="n">
+        <v>3.506999969482422</v>
+      </c>
+      <c r="D206" t="n">
+        <v>3.289999961853027</v>
+      </c>
+      <c r="E206" t="n">
+        <v>3.438999891281128</v>
+      </c>
+      <c r="F206" t="n">
+        <v>157089</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="n">
+        <v>45954</v>
+      </c>
+      <c r="B207" t="n">
+        <v>3.303999900817871</v>
+      </c>
+      <c r="C207" t="n">
+        <v>3.397000074386597</v>
+      </c>
+      <c r="D207" t="n">
+        <v>3.200000047683716</v>
+      </c>
+      <c r="E207" t="n">
+        <v>3.285000085830688</v>
+      </c>
+      <c r="F207" t="n">
+        <v>157089</v>
       </c>
     </row>
   </sheetData>

--- a/data/lng_2025_price.xlsx
+++ b/data/lng_2025_price.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F207"/>
+  <dimension ref="A1:F223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4581,7 +4581,327 @@
         <v>3.285000085830688</v>
       </c>
       <c r="F207" t="n">
-        <v>157089</v>
+        <v>108141</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="n">
+        <v>45957</v>
+      </c>
+      <c r="B208" t="n">
+        <v>3.441999912261963</v>
+      </c>
+      <c r="C208" t="n">
+        <v>3.469000101089478</v>
+      </c>
+      <c r="D208" t="n">
+        <v>3.260999917984009</v>
+      </c>
+      <c r="E208" t="n">
+        <v>3.410000085830688</v>
+      </c>
+      <c r="F208" t="n">
+        <v>67444</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="n">
+        <v>45958</v>
+      </c>
+      <c r="B209" t="n">
+        <v>3.345000028610229</v>
+      </c>
+      <c r="C209" t="n">
+        <v>3.434999942779541</v>
+      </c>
+      <c r="D209" t="n">
+        <v>3.239000082015991</v>
+      </c>
+      <c r="E209" t="n">
+        <v>3.41100001335144</v>
+      </c>
+      <c r="F209" t="n">
+        <v>85022</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="n">
+        <v>45959</v>
+      </c>
+      <c r="B210" t="n">
+        <v>3.375999927520752</v>
+      </c>
+      <c r="C210" t="n">
+        <v>3.404999971389771</v>
+      </c>
+      <c r="D210" t="n">
+        <v>3.193000078201294</v>
+      </c>
+      <c r="E210" t="n">
+        <v>3.270999908447266</v>
+      </c>
+      <c r="F210" t="n">
+        <v>153684</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="n">
+        <v>45960</v>
+      </c>
+      <c r="B211" t="n">
+        <v>3.956000089645386</v>
+      </c>
+      <c r="C211" t="n">
+        <v>4.071000099182129</v>
+      </c>
+      <c r="D211" t="n">
+        <v>3.78600001335144</v>
+      </c>
+      <c r="E211" t="n">
+        <v>3.79800009727478</v>
+      </c>
+      <c r="F211" t="n">
+        <v>201075</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="n">
+        <v>45961</v>
+      </c>
+      <c r="B212" t="n">
+        <v>4.124000072479248</v>
+      </c>
+      <c r="C212" t="n">
+        <v>4.157000064849854</v>
+      </c>
+      <c r="D212" t="n">
+        <v>4.014999866485596</v>
+      </c>
+      <c r="E212" t="n">
+        <v>4.060999870300293</v>
+      </c>
+      <c r="F212" t="n">
+        <v>238492</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="n">
+        <v>45964</v>
+      </c>
+      <c r="B213" t="n">
+        <v>4.265999794006348</v>
+      </c>
+      <c r="C213" t="n">
+        <v>4.297999858856201</v>
+      </c>
+      <c r="D213" t="n">
+        <v>4.086999893188477</v>
+      </c>
+      <c r="E213" t="n">
+        <v>4.159999847412109</v>
+      </c>
+      <c r="F213" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="B214" t="n">
+        <v>4.342999935150146</v>
+      </c>
+      <c r="C214" t="n">
+        <v>4.395999908447266</v>
+      </c>
+      <c r="D214" t="n">
+        <v>4.183000087738037</v>
+      </c>
+      <c r="E214" t="n">
+        <v>4.25600004196167</v>
+      </c>
+      <c r="F214" t="n">
+        <v>231288</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="B215" t="n">
+        <v>4.23199987411499</v>
+      </c>
+      <c r="C215" t="n">
+        <v>4.35099983215332</v>
+      </c>
+      <c r="D215" t="n">
+        <v>4.205999851226807</v>
+      </c>
+      <c r="E215" t="n">
+        <v>4.320000171661377</v>
+      </c>
+      <c r="F215" t="n">
+        <v>156270</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B216" t="n">
+        <v>4.35699987411499</v>
+      </c>
+      <c r="C216" t="n">
+        <v>4.420000076293945</v>
+      </c>
+      <c r="D216" t="n">
+        <v>4.191999912261963</v>
+      </c>
+      <c r="E216" t="n">
+        <v>4.238999843597412</v>
+      </c>
+      <c r="F216" t="n">
+        <v>193866</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="n">
+        <v>45968</v>
+      </c>
+      <c r="B217" t="n">
+        <v>4.315000057220459</v>
+      </c>
+      <c r="C217" t="n">
+        <v>4.419000148773193</v>
+      </c>
+      <c r="D217" t="n">
+        <v>4.26800012588501</v>
+      </c>
+      <c r="E217" t="n">
+        <v>4.413000106811523</v>
+      </c>
+      <c r="F217" t="n">
+        <v>178319</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="n">
+        <v>45971</v>
+      </c>
+      <c r="B218" t="n">
+        <v>4.337999820709229</v>
+      </c>
+      <c r="C218" t="n">
+        <v>4.508999824523926</v>
+      </c>
+      <c r="D218" t="n">
+        <v>4.26200008392334</v>
+      </c>
+      <c r="E218" t="n">
+        <v>4.480000019073486</v>
+      </c>
+      <c r="F218" t="n">
+        <v>189080</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="n">
+        <v>45972</v>
+      </c>
+      <c r="B219" t="n">
+        <v>4.565000057220459</v>
+      </c>
+      <c r="C219" t="n">
+        <v>4.580999851226807</v>
+      </c>
+      <c r="D219" t="n">
+        <v>4.276000022888184</v>
+      </c>
+      <c r="E219" t="n">
+        <v>4.375</v>
+      </c>
+      <c r="F219" t="n">
+        <v>243691</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="n">
+        <v>45973</v>
+      </c>
+      <c r="B220" t="n">
+        <v>4.532999992370605</v>
+      </c>
+      <c r="C220" t="n">
+        <v>4.581999778747559</v>
+      </c>
+      <c r="D220" t="n">
+        <v>4.460999965667725</v>
+      </c>
+      <c r="E220" t="n">
+        <v>4.526000022888184</v>
+      </c>
+      <c r="F220" t="n">
+        <v>170351</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="n">
+        <v>45974</v>
+      </c>
+      <c r="B221" t="n">
+        <v>4.645999908447266</v>
+      </c>
+      <c r="C221" t="n">
+        <v>4.688000202178955</v>
+      </c>
+      <c r="D221" t="n">
+        <v>4.453999996185303</v>
+      </c>
+      <c r="E221" t="n">
+        <v>4.534999847412109</v>
+      </c>
+      <c r="F221" t="n">
+        <v>201019</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="n">
+        <v>45975</v>
+      </c>
+      <c r="B222" t="n">
+        <v>4.565999984741211</v>
+      </c>
+      <c r="C222" t="n">
+        <v>4.635000228881836</v>
+      </c>
+      <c r="D222" t="n">
+        <v>4.375999927520752</v>
+      </c>
+      <c r="E222" t="n">
+        <v>4.597000122070312</v>
+      </c>
+      <c r="F222" t="n">
+        <v>227908</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="n">
+        <v>45978</v>
+      </c>
+      <c r="B223" t="n">
+        <v>4.361000061035156</v>
+      </c>
+      <c r="C223" t="n">
+        <v>4.540999889373779</v>
+      </c>
+      <c r="D223" t="n">
+        <v>4.322999954223633</v>
+      </c>
+      <c r="E223" t="n">
+        <v>4.531000137329102</v>
+      </c>
+      <c r="F223" t="n">
+        <v>227908</v>
       </c>
     </row>
   </sheetData>

--- a/data/lng_2025_price.xlsx
+++ b/data/lng_2025_price.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F223"/>
+  <dimension ref="A1:F249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4901,7 +4901,527 @@
         <v>4.531000137329102</v>
       </c>
       <c r="F223" t="n">
-        <v>227908</v>
+        <v>191623</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="n">
+        <v>45979</v>
+      </c>
+      <c r="B224" t="n">
+        <v>4.370999813079834</v>
+      </c>
+      <c r="C224" t="n">
+        <v>4.401000022888184</v>
+      </c>
+      <c r="D224" t="n">
+        <v>4.235000133514404</v>
+      </c>
+      <c r="E224" t="n">
+        <v>4.342000007629395</v>
+      </c>
+      <c r="F224" t="n">
+        <v>204812</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="n">
+        <v>45980</v>
+      </c>
+      <c r="B225" t="n">
+        <v>4.550000190734863</v>
+      </c>
+      <c r="C225" t="n">
+        <v>4.60200023651123</v>
+      </c>
+      <c r="D225" t="n">
+        <v>4.349999904632568</v>
+      </c>
+      <c r="E225" t="n">
+        <v>4.374000072479248</v>
+      </c>
+      <c r="F225" t="n">
+        <v>152272</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="n">
+        <v>45981</v>
+      </c>
+      <c r="B226" t="n">
+        <v>4.473999977111816</v>
+      </c>
+      <c r="C226" t="n">
+        <v>4.611999988555908</v>
+      </c>
+      <c r="D226" t="n">
+        <v>4.458000183105469</v>
+      </c>
+      <c r="E226" t="n">
+        <v>4.565999984741211</v>
+      </c>
+      <c r="F226" t="n">
+        <v>105538</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="n">
+        <v>45982</v>
+      </c>
+      <c r="B227" t="n">
+        <v>4.579999923706055</v>
+      </c>
+      <c r="C227" t="n">
+        <v>4.675000190734863</v>
+      </c>
+      <c r="D227" t="n">
+        <v>4.460999965667725</v>
+      </c>
+      <c r="E227" t="n">
+        <v>4.488999843597412</v>
+      </c>
+      <c r="F227" t="n">
+        <v>80707</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="n">
+        <v>45985</v>
+      </c>
+      <c r="B228" t="n">
+        <v>4.548999786376953</v>
+      </c>
+      <c r="C228" t="n">
+        <v>4.576000213623047</v>
+      </c>
+      <c r="D228" t="n">
+        <v>4.443999767303467</v>
+      </c>
+      <c r="E228" t="n">
+        <v>4.465000152587891</v>
+      </c>
+      <c r="F228" t="n">
+        <v>78483</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="n">
+        <v>45986</v>
+      </c>
+      <c r="B229" t="n">
+        <v>4.423999786376953</v>
+      </c>
+      <c r="C229" t="n">
+        <v>4.546999931335449</v>
+      </c>
+      <c r="D229" t="n">
+        <v>4.267000198364258</v>
+      </c>
+      <c r="E229" t="n">
+        <v>4.500999927520752</v>
+      </c>
+      <c r="F229" t="n">
+        <v>240457</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="n">
+        <v>45987</v>
+      </c>
+      <c r="B230" t="n">
+        <v>4.558000087738037</v>
+      </c>
+      <c r="C230" t="n">
+        <v>4.644000053405762</v>
+      </c>
+      <c r="D230" t="n">
+        <v>4.441999912261963</v>
+      </c>
+      <c r="E230" t="n">
+        <v>4.482999801635742</v>
+      </c>
+      <c r="F230" t="n">
+        <v>155159</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="n">
+        <v>45989</v>
+      </c>
+      <c r="B231" t="n">
+        <v>4.849999904632568</v>
+      </c>
+      <c r="C231" t="n">
+        <v>4.870999813079834</v>
+      </c>
+      <c r="D231" t="n">
+        <v>4.526999950408936</v>
+      </c>
+      <c r="E231" t="n">
+        <v>4.618000030517578</v>
+      </c>
+      <c r="F231" t="n">
+        <v>127694</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B232" t="n">
+        <v>4.921000003814697</v>
+      </c>
+      <c r="C232" t="n">
+        <v>4.952000141143799</v>
+      </c>
+      <c r="D232" t="n">
+        <v>4.757999897003174</v>
+      </c>
+      <c r="E232" t="n">
+        <v>4.869999885559082</v>
+      </c>
+      <c r="F232" t="n">
+        <v>209469</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="n">
+        <v>45993</v>
+      </c>
+      <c r="B233" t="n">
+        <v>4.840000152587891</v>
+      </c>
+      <c r="C233" t="n">
+        <v>4.984000205993652</v>
+      </c>
+      <c r="D233" t="n">
+        <v>4.804999828338623</v>
+      </c>
+      <c r="E233" t="n">
+        <v>4.901999950408936</v>
+      </c>
+      <c r="F233" t="n">
+        <v>172375</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="n">
+        <v>45994</v>
+      </c>
+      <c r="B234" t="n">
+        <v>4.994999885559082</v>
+      </c>
+      <c r="C234" t="n">
+        <v>5.039000034332275</v>
+      </c>
+      <c r="D234" t="n">
+        <v>4.818999767303467</v>
+      </c>
+      <c r="E234" t="n">
+        <v>4.827000141143799</v>
+      </c>
+      <c r="F234" t="n">
+        <v>186366</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="n">
+        <v>45995</v>
+      </c>
+      <c r="B235" t="n">
+        <v>5.063000202178955</v>
+      </c>
+      <c r="C235" t="n">
+        <v>5.090000152587891</v>
+      </c>
+      <c r="D235" t="n">
+        <v>4.870999813079834</v>
+      </c>
+      <c r="E235" t="n">
+        <v>5.010000228881836</v>
+      </c>
+      <c r="F235" t="n">
+        <v>209843</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="B236" t="n">
+        <v>5.289000034332275</v>
+      </c>
+      <c r="C236" t="n">
+        <v>5.495999813079834</v>
+      </c>
+      <c r="D236" t="n">
+        <v>5.026999950408936</v>
+      </c>
+      <c r="E236" t="n">
+        <v>5.077000141143799</v>
+      </c>
+      <c r="F236" t="n">
+        <v>376679</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="n">
+        <v>45999</v>
+      </c>
+      <c r="B237" t="n">
+        <v>4.912000179290771</v>
+      </c>
+      <c r="C237" t="n">
+        <v>5.204999923706055</v>
+      </c>
+      <c r="D237" t="n">
+        <v>4.849999904632568</v>
+      </c>
+      <c r="E237" t="n">
+        <v>5.099999904632568</v>
+      </c>
+      <c r="F237" t="n">
+        <v>301953</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="n">
+        <v>46000</v>
+      </c>
+      <c r="B238" t="n">
+        <v>4.573999881744385</v>
+      </c>
+      <c r="C238" t="n">
+        <v>4.877999782562256</v>
+      </c>
+      <c r="D238" t="n">
+        <v>4.551000118255615</v>
+      </c>
+      <c r="E238" t="n">
+        <v>4.868000030517578</v>
+      </c>
+      <c r="F238" t="n">
+        <v>249501</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="n">
+        <v>46001</v>
+      </c>
+      <c r="B239" t="n">
+        <v>4.59499979019165</v>
+      </c>
+      <c r="C239" t="n">
+        <v>4.696000099182129</v>
+      </c>
+      <c r="D239" t="n">
+        <v>4.454999923706055</v>
+      </c>
+      <c r="E239" t="n">
+        <v>4.578000068664551</v>
+      </c>
+      <c r="F239" t="n">
+        <v>271105</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="n">
+        <v>46002</v>
+      </c>
+      <c r="B240" t="n">
+        <v>4.230999946594238</v>
+      </c>
+      <c r="C240" t="n">
+        <v>4.63100004196167</v>
+      </c>
+      <c r="D240" t="n">
+        <v>4.196000099182129</v>
+      </c>
+      <c r="E240" t="n">
+        <v>4.625999927520752</v>
+      </c>
+      <c r="F240" t="n">
+        <v>287859</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="n">
+        <v>46003</v>
+      </c>
+      <c r="B241" t="n">
+        <v>4.11299991607666</v>
+      </c>
+      <c r="C241" t="n">
+        <v>4.256999969482422</v>
+      </c>
+      <c r="D241" t="n">
+        <v>4.065000057220459</v>
+      </c>
+      <c r="E241" t="n">
+        <v>4.230999946594238</v>
+      </c>
+      <c r="F241" t="n">
+        <v>199844</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B242" t="n">
+        <v>4.01200008392334</v>
+      </c>
+      <c r="C242" t="n">
+        <v>4.217999935150146</v>
+      </c>
+      <c r="D242" t="n">
+        <v>3.993000030517578</v>
+      </c>
+      <c r="E242" t="n">
+        <v>4.171000003814697</v>
+      </c>
+      <c r="F242" t="n">
+        <v>169239</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="n">
+        <v>46007</v>
+      </c>
+      <c r="B243" t="n">
+        <v>3.885999917984009</v>
+      </c>
+      <c r="C243" t="n">
+        <v>4.045000076293945</v>
+      </c>
+      <c r="D243" t="n">
+        <v>3.842000007629395</v>
+      </c>
+      <c r="E243" t="n">
+        <v>4.037000179290771</v>
+      </c>
+      <c r="F243" t="n">
+        <v>155859</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="n">
+        <v>46008</v>
+      </c>
+      <c r="B244" t="n">
+        <v>4.02400016784668</v>
+      </c>
+      <c r="C244" t="n">
+        <v>4.113999843597412</v>
+      </c>
+      <c r="D244" t="n">
+        <v>3.920000076293945</v>
+      </c>
+      <c r="E244" t="n">
+        <v>3.936000108718872</v>
+      </c>
+      <c r="F244" t="n">
+        <v>153559</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B245" t="n">
+        <v>3.907999992370605</v>
+      </c>
+      <c r="C245" t="n">
+        <v>4.217999935150146</v>
+      </c>
+      <c r="D245" t="n">
+        <v>3.877000093460083</v>
+      </c>
+      <c r="E245" t="n">
+        <v>4.117000102996826</v>
+      </c>
+      <c r="F245" t="n">
+        <v>158058</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="n">
+        <v>46010</v>
+      </c>
+      <c r="B246" t="n">
+        <v>3.983999967575073</v>
+      </c>
+      <c r="C246" t="n">
+        <v>4.03000020980835</v>
+      </c>
+      <c r="D246" t="n">
+        <v>3.839999914169312</v>
+      </c>
+      <c r="E246" t="n">
+        <v>3.941999912261963</v>
+      </c>
+      <c r="F246" t="n">
+        <v>145508</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="n">
+        <v>46013</v>
+      </c>
+      <c r="B247" t="n">
+        <v>3.964999914169312</v>
+      </c>
+      <c r="C247" t="n">
+        <v>4.139999866485596</v>
+      </c>
+      <c r="D247" t="n">
+        <v>3.796999931335449</v>
+      </c>
+      <c r="E247" t="n">
+        <v>4.080999851226807</v>
+      </c>
+      <c r="F247" t="n">
+        <v>157602</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="n">
+        <v>46014</v>
+      </c>
+      <c r="B248" t="n">
+        <v>4.407999992370605</v>
+      </c>
+      <c r="C248" t="n">
+        <v>4.448999881744385</v>
+      </c>
+      <c r="D248" t="n">
+        <v>3.943000078201294</v>
+      </c>
+      <c r="E248" t="n">
+        <v>3.990000009536743</v>
+      </c>
+      <c r="F248" t="n">
+        <v>126794</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="n">
+        <v>46015</v>
+      </c>
+      <c r="B249" t="n">
+        <v>4.242000102996826</v>
+      </c>
+      <c r="C249" t="n">
+        <v>4.592999935150146</v>
+      </c>
+      <c r="D249" t="n">
+        <v>4.179999828338623</v>
+      </c>
+      <c r="E249" t="n">
+        <v>4.414999961853027</v>
+      </c>
+      <c r="F249" t="n">
+        <v>126794</v>
       </c>
     </row>
   </sheetData>

--- a/data/lng_2025_price.xlsx
+++ b/data/lng_2025_price.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F249"/>
+  <dimension ref="A1:F273"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5421,7 +5421,487 @@
         <v>4.414999961853027</v>
       </c>
       <c r="F249" t="n">
-        <v>126794</v>
+        <v>57070</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="n">
+        <v>46017</v>
+      </c>
+      <c r="B250" t="n">
+        <v>4.366000175476074</v>
+      </c>
+      <c r="C250" t="n">
+        <v>4.421000003814697</v>
+      </c>
+      <c r="D250" t="n">
+        <v>4.196000099182129</v>
+      </c>
+      <c r="E250" t="n">
+        <v>4.196000099182129</v>
+      </c>
+      <c r="F250" t="n">
+        <v>46351</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="n">
+        <v>46020</v>
+      </c>
+      <c r="B251" t="n">
+        <v>4.686999797821045</v>
+      </c>
+      <c r="C251" t="n">
+        <v>4.721000194549561</v>
+      </c>
+      <c r="D251" t="n">
+        <v>4.35099983215332</v>
+      </c>
+      <c r="E251" t="n">
+        <v>4.449999809265137</v>
+      </c>
+      <c r="F251" t="n">
+        <v>163457</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="B252" t="n">
+        <v>3.971999883651733</v>
+      </c>
+      <c r="C252" t="n">
+        <v>4.176000118255615</v>
+      </c>
+      <c r="D252" t="n">
+        <v>3.915999889373779</v>
+      </c>
+      <c r="E252" t="n">
+        <v>3.947000026702881</v>
+      </c>
+      <c r="F252" t="n">
+        <v>136981</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B253" t="n">
+        <v>3.686000108718872</v>
+      </c>
+      <c r="C253" t="n">
+        <v>3.983000040054321</v>
+      </c>
+      <c r="D253" t="n">
+        <v>3.678999900817871</v>
+      </c>
+      <c r="E253" t="n">
+        <v>3.976000070571899</v>
+      </c>
+      <c r="F253" t="n">
+        <v>132231</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="n">
+        <v>46024</v>
+      </c>
+      <c r="B254" t="n">
+        <v>3.618000030517578</v>
+      </c>
+      <c r="C254" t="n">
+        <v>3.703000068664551</v>
+      </c>
+      <c r="D254" t="n">
+        <v>3.562999963760376</v>
+      </c>
+      <c r="E254" t="n">
+        <v>3.678999900817871</v>
+      </c>
+      <c r="F254" t="n">
+        <v>133024</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="n">
+        <v>46027</v>
+      </c>
+      <c r="B255" t="n">
+        <v>3.523000001907349</v>
+      </c>
+      <c r="C255" t="n">
+        <v>3.529999971389771</v>
+      </c>
+      <c r="D255" t="n">
+        <v>3.355000019073486</v>
+      </c>
+      <c r="E255" t="n">
+        <v>3.506999969482422</v>
+      </c>
+      <c r="F255" t="n">
+        <v>228737</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="n">
+        <v>46028</v>
+      </c>
+      <c r="B256" t="n">
+        <v>3.349999904632568</v>
+      </c>
+      <c r="C256" t="n">
+        <v>3.502000093460083</v>
+      </c>
+      <c r="D256" t="n">
+        <v>3.323999881744385</v>
+      </c>
+      <c r="E256" t="n">
+        <v>3.492000102996826</v>
+      </c>
+      <c r="F256" t="n">
+        <v>145165</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="n">
+        <v>46029</v>
+      </c>
+      <c r="B257" t="n">
+        <v>3.525000095367432</v>
+      </c>
+      <c r="C257" t="n">
+        <v>3.591000080108643</v>
+      </c>
+      <c r="D257" t="n">
+        <v>3.418999910354614</v>
+      </c>
+      <c r="E257" t="n">
+        <v>3.424999952316284</v>
+      </c>
+      <c r="F257" t="n">
+        <v>151941</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="n">
+        <v>46030</v>
+      </c>
+      <c r="B258" t="n">
+        <v>3.407000064849854</v>
+      </c>
+      <c r="C258" t="n">
+        <v>3.634000062942505</v>
+      </c>
+      <c r="D258" t="n">
+        <v>3.355000019073486</v>
+      </c>
+      <c r="E258" t="n">
+        <v>3.562999963760376</v>
+      </c>
+      <c r="F258" t="n">
+        <v>193218</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="n">
+        <v>46031</v>
+      </c>
+      <c r="B259" t="n">
+        <v>3.168999910354614</v>
+      </c>
+      <c r="C259" t="n">
+        <v>3.496000051498413</v>
+      </c>
+      <c r="D259" t="n">
+        <v>3.13100004196167</v>
+      </c>
+      <c r="E259" t="n">
+        <v>3.410000085830688</v>
+      </c>
+      <c r="F259" t="n">
+        <v>322218</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="n">
+        <v>46034</v>
+      </c>
+      <c r="B260" t="n">
+        <v>3.408999919891357</v>
+      </c>
+      <c r="C260" t="n">
+        <v>3.430999994277954</v>
+      </c>
+      <c r="D260" t="n">
+        <v>3.181999921798706</v>
+      </c>
+      <c r="E260" t="n">
+        <v>3.289999961853027</v>
+      </c>
+      <c r="F260" t="n">
+        <v>248893</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="n">
+        <v>46035</v>
+      </c>
+      <c r="B261" t="n">
+        <v>3.418999910354614</v>
+      </c>
+      <c r="C261" t="n">
+        <v>3.499000072479248</v>
+      </c>
+      <c r="D261" t="n">
+        <v>3.29800009727478</v>
+      </c>
+      <c r="E261" t="n">
+        <v>3.358000040054321</v>
+      </c>
+      <c r="F261" t="n">
+        <v>187132</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="n">
+        <v>46036</v>
+      </c>
+      <c r="B262" t="n">
+        <v>3.119999885559082</v>
+      </c>
+      <c r="C262" t="n">
+        <v>3.443000078201294</v>
+      </c>
+      <c r="D262" t="n">
+        <v>3.068000078201294</v>
+      </c>
+      <c r="E262" t="n">
+        <v>3.384000062942505</v>
+      </c>
+      <c r="F262" t="n">
+        <v>215332</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="n">
+        <v>46037</v>
+      </c>
+      <c r="B263" t="n">
+        <v>3.128000020980835</v>
+      </c>
+      <c r="C263" t="n">
+        <v>3.217999935150146</v>
+      </c>
+      <c r="D263" t="n">
+        <v>3.00600004196167</v>
+      </c>
+      <c r="E263" t="n">
+        <v>3.101999998092651</v>
+      </c>
+      <c r="F263" t="n">
+        <v>180723</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="n">
+        <v>46038</v>
+      </c>
+      <c r="B264" t="n">
+        <v>3.102999925613403</v>
+      </c>
+      <c r="C264" t="n">
+        <v>3.230000019073486</v>
+      </c>
+      <c r="D264" t="n">
+        <v>3.019999980926514</v>
+      </c>
+      <c r="E264" t="n">
+        <v>3.145999908447266</v>
+      </c>
+      <c r="F264" t="n">
+        <v>139667</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="n">
+        <v>46042</v>
+      </c>
+      <c r="B265" t="n">
+        <v>3.907000064849854</v>
+      </c>
+      <c r="C265" t="n">
+        <v>3.990000009536743</v>
+      </c>
+      <c r="D265" t="n">
+        <v>3.380000114440918</v>
+      </c>
+      <c r="E265" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F265" t="n">
+        <v>410520</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="n">
+        <v>46043</v>
+      </c>
+      <c r="B266" t="n">
+        <v>4.875</v>
+      </c>
+      <c r="C266" t="n">
+        <v>5.098999977111816</v>
+      </c>
+      <c r="D266" t="n">
+        <v>3.834000110626221</v>
+      </c>
+      <c r="E266" t="n">
+        <v>3.903000116348267</v>
+      </c>
+      <c r="F266" t="n">
+        <v>367003</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="n">
+        <v>46044</v>
+      </c>
+      <c r="B267" t="n">
+        <v>5.045000076293945</v>
+      </c>
+      <c r="C267" t="n">
+        <v>5.650000095367432</v>
+      </c>
+      <c r="D267" t="n">
+        <v>4.769000053405762</v>
+      </c>
+      <c r="E267" t="n">
+        <v>5.039000034332275</v>
+      </c>
+      <c r="F267" t="n">
+        <v>310947</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="n">
+        <v>46045</v>
+      </c>
+      <c r="B268" t="n">
+        <v>5.275000095367432</v>
+      </c>
+      <c r="C268" t="n">
+        <v>5.434000015258789</v>
+      </c>
+      <c r="D268" t="n">
+        <v>4.659999847412109</v>
+      </c>
+      <c r="E268" t="n">
+        <v>4.872000217437744</v>
+      </c>
+      <c r="F268" t="n">
+        <v>107108</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="n">
+        <v>46048</v>
+      </c>
+      <c r="B269" t="n">
+        <v>6.800000190734863</v>
+      </c>
+      <c r="C269" t="n">
+        <v>7.439000129699707</v>
+      </c>
+      <c r="D269" t="n">
+        <v>5.728000164031982</v>
+      </c>
+      <c r="E269" t="n">
+        <v>5.790999889373779</v>
+      </c>
+      <c r="F269" t="n">
+        <v>99498</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="n">
+        <v>46049</v>
+      </c>
+      <c r="B270" t="n">
+        <v>6.953999996185303</v>
+      </c>
+      <c r="C270" t="n">
+        <v>7.309999942779541</v>
+      </c>
+      <c r="D270" t="n">
+        <v>5.771999835968018</v>
+      </c>
+      <c r="E270" t="n">
+        <v>6.645999908447266</v>
+      </c>
+      <c r="F270" t="n">
+        <v>77676</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="2" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B271" t="n">
+        <v>7.460000038146973</v>
+      </c>
+      <c r="C271" t="n">
+        <v>7.827000141143799</v>
+      </c>
+      <c r="D271" t="n">
+        <v>5.900000095367432</v>
+      </c>
+      <c r="E271" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F271" t="n">
+        <v>235065</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="2" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B272" t="n">
+        <v>3.917999982833862</v>
+      </c>
+      <c r="C272" t="n">
+        <v>3.930000066757202</v>
+      </c>
+      <c r="D272" t="n">
+        <v>3.727999925613403</v>
+      </c>
+      <c r="E272" t="n">
+        <v>3.742000102996826</v>
+      </c>
+      <c r="F272" t="n">
+        <v>234642</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B273" t="n">
+        <v>4.354000091552734</v>
+      </c>
+      <c r="C273" t="n">
+        <v>4.425000190734863</v>
+      </c>
+      <c r="D273" t="n">
+        <v>3.818000078201294</v>
+      </c>
+      <c r="E273" t="n">
+        <v>3.878999948501587</v>
+      </c>
+      <c r="F273" t="n">
+        <v>234642</v>
       </c>
     </row>
   </sheetData>

--- a/data/lng_2025_price.xlsx
+++ b/data/lng_2025_price.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F273"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,401 +466,5441 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46024</v>
+        <v>45659</v>
       </c>
       <c r="B2" t="n">
-        <v>3.618000030517578</v>
+        <v>3.660000085830688</v>
       </c>
       <c r="C2" t="n">
-        <v>3.703000068664551</v>
+        <v>3.801000118255615</v>
       </c>
       <c r="D2" t="n">
-        <v>3.562999963760376</v>
+        <v>3.540999889373779</v>
       </c>
       <c r="E2" t="n">
-        <v>3.678999900817871</v>
+        <v>3.655999898910522</v>
       </c>
       <c r="F2" t="n">
-        <v>133024</v>
+        <v>156670</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46027</v>
+        <v>45660</v>
       </c>
       <c r="B3" t="n">
-        <v>3.523000001907349</v>
+        <v>3.354000091552734</v>
       </c>
       <c r="C3" t="n">
-        <v>3.529999971389771</v>
+        <v>3.680000066757202</v>
       </c>
       <c r="D3" t="n">
-        <v>3.355000019073486</v>
+        <v>3.329999923706055</v>
       </c>
       <c r="E3" t="n">
-        <v>3.506999969482422</v>
+        <v>3.668999910354614</v>
       </c>
       <c r="F3" t="n">
-        <v>228737</v>
+        <v>188094</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46028</v>
+        <v>45663</v>
       </c>
       <c r="B4" t="n">
-        <v>3.349999904632568</v>
+        <v>3.671999931335449</v>
       </c>
       <c r="C4" t="n">
+        <v>3.726000070571899</v>
+      </c>
+      <c r="D4" t="n">
         <v>3.502000093460083</v>
       </c>
-      <c r="D4" t="n">
-        <v>3.323999881744385</v>
-      </c>
       <c r="E4" t="n">
-        <v>3.492000102996826</v>
+        <v>3.553999900817871</v>
       </c>
       <c r="F4" t="n">
-        <v>145165</v>
+        <v>228124</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>46029</v>
+        <v>45664</v>
       </c>
       <c r="B5" t="n">
-        <v>3.525000095367432</v>
+        <v>3.448999881744385</v>
       </c>
       <c r="C5" t="n">
-        <v>3.591000080108643</v>
+        <v>3.73799991607666</v>
       </c>
       <c r="D5" t="n">
-        <v>3.418999910354614</v>
+        <v>3.427000045776367</v>
       </c>
       <c r="E5" t="n">
-        <v>3.424999952316284</v>
+        <v>3.704999923706055</v>
       </c>
       <c r="F5" t="n">
-        <v>151941</v>
+        <v>182148</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>46030</v>
+        <v>45665</v>
       </c>
       <c r="B6" t="n">
-        <v>3.407000064849854</v>
+        <v>3.651000022888184</v>
       </c>
       <c r="C6" t="n">
-        <v>3.634000062942505</v>
+        <v>3.694000005722046</v>
       </c>
       <c r="D6" t="n">
-        <v>3.355000019073486</v>
+        <v>3.427000045776367</v>
       </c>
       <c r="E6" t="n">
-        <v>3.562999963760376</v>
+        <v>3.447999954223633</v>
       </c>
       <c r="F6" t="n">
-        <v>193218</v>
+        <v>189259</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>46031</v>
+        <v>45666</v>
       </c>
       <c r="B7" t="n">
-        <v>3.168999910354614</v>
+        <v>3.700999975204468</v>
       </c>
       <c r="C7" t="n">
-        <v>3.496000051498413</v>
+        <v>3.829999923706055</v>
       </c>
       <c r="D7" t="n">
-        <v>3.13100004196167</v>
+        <v>3.552000045776367</v>
       </c>
       <c r="E7" t="n">
-        <v>3.410000085830688</v>
+        <v>3.681999921798706</v>
       </c>
       <c r="F7" t="n">
-        <v>322218</v>
+        <v>145203</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>46034</v>
+        <v>45667</v>
       </c>
       <c r="B8" t="n">
-        <v>3.408999919891357</v>
+        <v>3.989000082015991</v>
       </c>
       <c r="C8" t="n">
-        <v>3.430999994277954</v>
+        <v>4.01800012588501</v>
       </c>
       <c r="D8" t="n">
-        <v>3.181999921798706</v>
+        <v>3.684999942779541</v>
       </c>
       <c r="E8" t="n">
-        <v>3.289999961853027</v>
+        <v>3.709000110626221</v>
       </c>
       <c r="F8" t="n">
-        <v>248893</v>
+        <v>229112</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>46035</v>
+        <v>45670</v>
       </c>
       <c r="B9" t="n">
-        <v>3.418999910354614</v>
+        <v>3.934000015258789</v>
       </c>
       <c r="C9" t="n">
-        <v>3.499000072479248</v>
+        <v>4.36899995803833</v>
       </c>
       <c r="D9" t="n">
-        <v>3.29800009727478</v>
+        <v>3.845000028610229</v>
       </c>
       <c r="E9" t="n">
-        <v>3.358000040054321</v>
+        <v>4.347000122070312</v>
       </c>
       <c r="F9" t="n">
-        <v>187132</v>
+        <v>195514</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>46036</v>
+        <v>45671</v>
       </c>
       <c r="B10" t="n">
-        <v>3.119999885559082</v>
+        <v>3.967999935150146</v>
       </c>
       <c r="C10" t="n">
-        <v>3.443000078201294</v>
+        <v>4.059000015258789</v>
       </c>
       <c r="D10" t="n">
-        <v>3.068000078201294</v>
+        <v>3.736000061035156</v>
       </c>
       <c r="E10" t="n">
-        <v>3.384000062942505</v>
+        <v>3.930000066757202</v>
       </c>
       <c r="F10" t="n">
-        <v>215332</v>
+        <v>167416</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>46037</v>
+        <v>45672</v>
       </c>
       <c r="B11" t="n">
-        <v>3.128000020980835</v>
+        <v>4.083000183105469</v>
       </c>
       <c r="C11" t="n">
-        <v>3.217999935150146</v>
+        <v>4.140999794006348</v>
       </c>
       <c r="D11" t="n">
-        <v>3.00600004196167</v>
+        <v>3.858999967575073</v>
       </c>
       <c r="E11" t="n">
-        <v>3.101999998092651</v>
+        <v>3.954999923706055</v>
       </c>
       <c r="F11" t="n">
-        <v>180723</v>
+        <v>169338</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>46038</v>
+        <v>45673</v>
       </c>
       <c r="B12" t="n">
-        <v>3.102999925613403</v>
+        <v>4.257999897003174</v>
       </c>
       <c r="C12" t="n">
-        <v>3.230000019073486</v>
+        <v>4.328000068664551</v>
       </c>
       <c r="D12" t="n">
-        <v>3.019999980926514</v>
+        <v>4.01800012588501</v>
       </c>
       <c r="E12" t="n">
-        <v>3.145999908447266</v>
+        <v>4.130000114440918</v>
       </c>
       <c r="F12" t="n">
-        <v>139667</v>
+        <v>193018</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>46042</v>
+        <v>45674</v>
       </c>
       <c r="B13" t="n">
-        <v>3.907000064849854</v>
+        <v>3.947999954223633</v>
       </c>
       <c r="C13" t="n">
-        <v>3.990000009536743</v>
+        <v>4.308000087738037</v>
       </c>
       <c r="D13" t="n">
-        <v>3.380000114440918</v>
+        <v>3.910000085830688</v>
       </c>
       <c r="E13" t="n">
-        <v>3.5</v>
+        <v>4.28000020980835</v>
       </c>
       <c r="F13" t="n">
-        <v>410520</v>
+        <v>204277</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>46043</v>
+        <v>45678</v>
       </c>
       <c r="B14" t="n">
-        <v>4.875</v>
+        <v>3.75600004196167</v>
       </c>
       <c r="C14" t="n">
-        <v>5.098999977111816</v>
+        <v>3.914000034332275</v>
       </c>
       <c r="D14" t="n">
-        <v>3.834000110626221</v>
+        <v>3.719000101089478</v>
       </c>
       <c r="E14" t="n">
-        <v>3.903000116348267</v>
+        <v>3.815000057220459</v>
       </c>
       <c r="F14" t="n">
-        <v>367003</v>
+        <v>209907</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>46044</v>
+        <v>45679</v>
       </c>
       <c r="B15" t="n">
-        <v>5.045000076293945</v>
+        <v>3.960000038146973</v>
       </c>
       <c r="C15" t="n">
-        <v>5.650000095367432</v>
+        <v>4.008999824523926</v>
       </c>
       <c r="D15" t="n">
-        <v>4.769000053405762</v>
+        <v>3.710999965667725</v>
       </c>
       <c r="E15" t="n">
-        <v>5.039000034332275</v>
+        <v>3.78600001335144</v>
       </c>
       <c r="F15" t="n">
-        <v>310947</v>
+        <v>128783</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>46045</v>
+        <v>45680</v>
       </c>
       <c r="B16" t="n">
-        <v>5.275000095367432</v>
+        <v>3.944999933242798</v>
       </c>
       <c r="C16" t="n">
-        <v>5.434000015258789</v>
+        <v>4.047999858856201</v>
       </c>
       <c r="D16" t="n">
-        <v>4.659999847412109</v>
+        <v>3.861000061035156</v>
       </c>
       <c r="E16" t="n">
-        <v>4.872000217437744</v>
+        <v>4.000999927520752</v>
       </c>
       <c r="F16" t="n">
-        <v>107108</v>
+        <v>120839</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>46048</v>
+        <v>45681</v>
       </c>
       <c r="B17" t="n">
-        <v>6.800000190734863</v>
+        <v>4.026999950408936</v>
       </c>
       <c r="C17" t="n">
-        <v>7.439000129699707</v>
+        <v>4.050000190734863</v>
       </c>
       <c r="D17" t="n">
-        <v>5.728000164031982</v>
+        <v>3.808000087738037</v>
       </c>
       <c r="E17" t="n">
-        <v>5.790999889373779</v>
+        <v>3.933000087738037</v>
       </c>
       <c r="F17" t="n">
-        <v>99498</v>
+        <v>87568</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>46049</v>
+        <v>45684</v>
       </c>
       <c r="B18" t="n">
-        <v>6.953999996185303</v>
+        <v>3.697000026702881</v>
       </c>
       <c r="C18" t="n">
-        <v>7.309999942779541</v>
+        <v>3.82699990272522</v>
       </c>
       <c r="D18" t="n">
-        <v>5.771999835968018</v>
+        <v>3.608999967575073</v>
       </c>
       <c r="E18" t="n">
-        <v>6.645999908447266</v>
+        <v>3.785000085830688</v>
       </c>
       <c r="F18" t="n">
-        <v>77676</v>
+        <v>66940</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>46050</v>
+        <v>45685</v>
       </c>
       <c r="B19" t="n">
-        <v>7.460000038146973</v>
+        <v>3.470999956130981</v>
       </c>
       <c r="C19" t="n">
-        <v>7.827000141143799</v>
+        <v>3.720000028610229</v>
       </c>
       <c r="D19" t="n">
-        <v>5.900000095367432</v>
+        <v>3.361000061035156</v>
       </c>
       <c r="E19" t="n">
-        <v>6.5</v>
+        <v>3.698999881744385</v>
       </c>
       <c r="F19" t="n">
-        <v>235065</v>
+        <v>63816</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>46051</v>
+        <v>45686</v>
       </c>
       <c r="B20" t="n">
-        <v>3.917999982833862</v>
+        <v>3.535000085830688</v>
       </c>
       <c r="C20" t="n">
-        <v>3.930000066757202</v>
+        <v>3.588000059127808</v>
       </c>
       <c r="D20" t="n">
-        <v>3.727999925613403</v>
+        <v>3.312999963760376</v>
       </c>
       <c r="E20" t="n">
-        <v>3.742000102996826</v>
+        <v>3.335000038146973</v>
       </c>
       <c r="F20" t="n">
-        <v>234642</v>
+        <v>167840</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
+        <v>45687</v>
+      </c>
+      <c r="B21" t="n">
+        <v>3.046999931335449</v>
+      </c>
+      <c r="C21" t="n">
+        <v>3.240000009536743</v>
+      </c>
+      <c r="D21" t="n">
+        <v>3.035000085830688</v>
+      </c>
+      <c r="E21" t="n">
+        <v>3.174999952316284</v>
+      </c>
+      <c r="F21" t="n">
+        <v>201741</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>45688</v>
+      </c>
+      <c r="B22" t="n">
+        <v>3.043999910354614</v>
+      </c>
+      <c r="C22" t="n">
+        <v>3.118000030517578</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.990000009536743</v>
+      </c>
+      <c r="E22" t="n">
+        <v>3.081000089645386</v>
+      </c>
+      <c r="F22" t="n">
+        <v>138212</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>45691</v>
+      </c>
+      <c r="B23" t="n">
+        <v>3.351999998092651</v>
+      </c>
+      <c r="C23" t="n">
+        <v>3.407000064849854</v>
+      </c>
+      <c r="D23" t="n">
+        <v>3.230000019073486</v>
+      </c>
+      <c r="E23" t="n">
+        <v>3.230000019073486</v>
+      </c>
+      <c r="F23" t="n">
+        <v>273510</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>45692</v>
+      </c>
+      <c r="B24" t="n">
+        <v>3.253000020980835</v>
+      </c>
+      <c r="C24" t="n">
+        <v>3.349999904632568</v>
+      </c>
+      <c r="D24" t="n">
+        <v>3.167999982833862</v>
+      </c>
+      <c r="E24" t="n">
+        <v>3.32699990272522</v>
+      </c>
+      <c r="F24" t="n">
+        <v>182531</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>45693</v>
+      </c>
+      <c r="B25" t="n">
+        <v>3.359999895095825</v>
+      </c>
+      <c r="C25" t="n">
+        <v>3.375</v>
+      </c>
+      <c r="D25" t="n">
+        <v>3.16100001335144</v>
+      </c>
+      <c r="E25" t="n">
+        <v>3.229000091552734</v>
+      </c>
+      <c r="F25" t="n">
+        <v>170256</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>45694</v>
+      </c>
+      <c r="B26" t="n">
+        <v>3.407999992370605</v>
+      </c>
+      <c r="C26" t="n">
+        <v>3.434000015258789</v>
+      </c>
+      <c r="D26" t="n">
+        <v>3.302999973297119</v>
+      </c>
+      <c r="E26" t="n">
+        <v>3.355000019073486</v>
+      </c>
+      <c r="F26" t="n">
+        <v>177672</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>45695</v>
+      </c>
+      <c r="B27" t="n">
+        <v>3.309000015258789</v>
+      </c>
+      <c r="C27" t="n">
+        <v>3.434999942779541</v>
+      </c>
+      <c r="D27" t="n">
+        <v>3.296000003814697</v>
+      </c>
+      <c r="E27" t="n">
+        <v>3.380000114440918</v>
+      </c>
+      <c r="F27" t="n">
+        <v>188698</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>45698</v>
+      </c>
+      <c r="B28" t="n">
+        <v>3.444000005722046</v>
+      </c>
+      <c r="C28" t="n">
+        <v>3.486999988555908</v>
+      </c>
+      <c r="D28" t="n">
+        <v>3.351999998092651</v>
+      </c>
+      <c r="E28" t="n">
+        <v>3.405999898910522</v>
+      </c>
+      <c r="F28" t="n">
+        <v>203924</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>45699</v>
+      </c>
+      <c r="B29" t="n">
+        <v>3.519000053405762</v>
+      </c>
+      <c r="C29" t="n">
+        <v>3.575999975204468</v>
+      </c>
+      <c r="D29" t="n">
+        <v>3.430999994277954</v>
+      </c>
+      <c r="E29" t="n">
+        <v>3.441999912261963</v>
+      </c>
+      <c r="F29" t="n">
+        <v>219162</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>45700</v>
+      </c>
+      <c r="B30" t="n">
+        <v>3.565000057220459</v>
+      </c>
+      <c r="C30" t="n">
+        <v>3.58299994468689</v>
+      </c>
+      <c r="D30" t="n">
+        <v>3.469000101089478</v>
+      </c>
+      <c r="E30" t="n">
+        <v>3.509999990463257</v>
+      </c>
+      <c r="F30" t="n">
+        <v>194725</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>45701</v>
+      </c>
+      <c r="B31" t="n">
+        <v>3.628000020980835</v>
+      </c>
+      <c r="C31" t="n">
+        <v>3.78600001335144</v>
+      </c>
+      <c r="D31" t="n">
+        <v>3.58299994468689</v>
+      </c>
+      <c r="E31" t="n">
+        <v>3.591000080108643</v>
+      </c>
+      <c r="F31" t="n">
+        <v>305899</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>45702</v>
+      </c>
+      <c r="B32" t="n">
+        <v>3.724999904632568</v>
+      </c>
+      <c r="C32" t="n">
+        <v>3.801000118255615</v>
+      </c>
+      <c r="D32" t="n">
+        <v>3.634999990463257</v>
+      </c>
+      <c r="E32" t="n">
+        <v>3.650000095367432</v>
+      </c>
+      <c r="F32" t="n">
+        <v>201102</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>45706</v>
+      </c>
+      <c r="B33" t="n">
+        <v>4.006999969482422</v>
+      </c>
+      <c r="C33" t="n">
+        <v>4.017000198364258</v>
+      </c>
+      <c r="D33" t="n">
+        <v>3.553999900817871</v>
+      </c>
+      <c r="E33" t="n">
+        <v>3.614000082015991</v>
+      </c>
+      <c r="F33" t="n">
+        <v>300505</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="B34" t="n">
+        <v>4.28000020980835</v>
+      </c>
+      <c r="C34" t="n">
+        <v>4.394000053405762</v>
+      </c>
+      <c r="D34" t="n">
+        <v>3.947000026702881</v>
+      </c>
+      <c r="E34" t="n">
+        <v>4.013000011444092</v>
+      </c>
+      <c r="F34" t="n">
+        <v>338827</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>45708</v>
+      </c>
+      <c r="B35" t="n">
+        <v>4.151999950408936</v>
+      </c>
+      <c r="C35" t="n">
+        <v>4.47599983215332</v>
+      </c>
+      <c r="D35" t="n">
+        <v>4.033999919891357</v>
+      </c>
+      <c r="E35" t="n">
+        <v>4.38100004196167</v>
+      </c>
+      <c r="F35" t="n">
+        <v>211817</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>45709</v>
+      </c>
+      <c r="B36" t="n">
+        <v>4.234000205993652</v>
+      </c>
+      <c r="C36" t="n">
+        <v>4.443999767303467</v>
+      </c>
+      <c r="D36" t="n">
+        <v>4.14799976348877</v>
+      </c>
+      <c r="E36" t="n">
+        <v>4.173999786376953</v>
+      </c>
+      <c r="F36" t="n">
+        <v>164320</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>45712</v>
+      </c>
+      <c r="B37" t="n">
+        <v>3.99399995803833</v>
+      </c>
+      <c r="C37" t="n">
+        <v>4.090000152587891</v>
+      </c>
+      <c r="D37" t="n">
+        <v>3.905999898910522</v>
+      </c>
+      <c r="E37" t="n">
+        <v>4.065000057220459</v>
+      </c>
+      <c r="F37" t="n">
+        <v>82872</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>45713</v>
+      </c>
+      <c r="B38" t="n">
+        <v>4.173999786376953</v>
+      </c>
+      <c r="C38" t="n">
+        <v>4.185999870300293</v>
+      </c>
+      <c r="D38" t="n">
+        <v>3.934999942779541</v>
+      </c>
+      <c r="E38" t="n">
+        <v>3.986999988555908</v>
+      </c>
+      <c r="F38" t="n">
+        <v>91529</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>45714</v>
+      </c>
+      <c r="B39" t="n">
+        <v>3.905999898910522</v>
+      </c>
+      <c r="C39" t="n">
+        <v>4.211999893188477</v>
+      </c>
+      <c r="D39" t="n">
+        <v>3.859999895095825</v>
+      </c>
+      <c r="E39" t="n">
+        <v>4.130000114440918</v>
+      </c>
+      <c r="F39" t="n">
+        <v>172826</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>45715</v>
+      </c>
+      <c r="B40" t="n">
+        <v>3.934000015258789</v>
+      </c>
+      <c r="C40" t="n">
+        <v>4.065000057220459</v>
+      </c>
+      <c r="D40" t="n">
+        <v>3.878000020980835</v>
+      </c>
+      <c r="E40" t="n">
+        <v>3.966000080108643</v>
+      </c>
+      <c r="F40" t="n">
+        <v>171402</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>45716</v>
+      </c>
+      <c r="B41" t="n">
+        <v>3.834000110626221</v>
+      </c>
+      <c r="C41" t="n">
+        <v>3.953999996185303</v>
+      </c>
+      <c r="D41" t="n">
+        <v>3.813999891281128</v>
+      </c>
+      <c r="E41" t="n">
+        <v>3.938999891281128</v>
+      </c>
+      <c r="F41" t="n">
+        <v>141989</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>45719</v>
+      </c>
+      <c r="B42" t="n">
+        <v>4.122000217437744</v>
+      </c>
+      <c r="C42" t="n">
+        <v>4.172999858856201</v>
+      </c>
+      <c r="D42" t="n">
+        <v>3.742000102996826</v>
+      </c>
+      <c r="E42" t="n">
+        <v>3.779000043869019</v>
+      </c>
+      <c r="F42" t="n">
+        <v>269838</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>45720</v>
+      </c>
+      <c r="B43" t="n">
+        <v>4.349999904632568</v>
+      </c>
+      <c r="C43" t="n">
+        <v>4.551000118255615</v>
+      </c>
+      <c r="D43" t="n">
+        <v>4.056000232696533</v>
+      </c>
+      <c r="E43" t="n">
+        <v>4.168000221252441</v>
+      </c>
+      <c r="F43" t="n">
+        <v>350513</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>45721</v>
+      </c>
+      <c r="B44" t="n">
+        <v>4.449999809265137</v>
+      </c>
+      <c r="C44" t="n">
+        <v>4.51800012588501</v>
+      </c>
+      <c r="D44" t="n">
+        <v>4.22700023651123</v>
+      </c>
+      <c r="E44" t="n">
+        <v>4.316999912261963</v>
+      </c>
+      <c r="F44" t="n">
+        <v>224571</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>45722</v>
+      </c>
+      <c r="B45" t="n">
+        <v>4.302000045776367</v>
+      </c>
+      <c r="C45" t="n">
+        <v>4.471000194549561</v>
+      </c>
+      <c r="D45" t="n">
+        <v>4.254000186920166</v>
+      </c>
+      <c r="E45" t="n">
+        <v>4.466000080108643</v>
+      </c>
+      <c r="F45" t="n">
+        <v>202475</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>45723</v>
+      </c>
+      <c r="B46" t="n">
+        <v>4.39900016784668</v>
+      </c>
+      <c r="C46" t="n">
+        <v>4.426000118255615</v>
+      </c>
+      <c r="D46" t="n">
+        <v>4.131999969482422</v>
+      </c>
+      <c r="E46" t="n">
+        <v>4.285999774932861</v>
+      </c>
+      <c r="F46" t="n">
+        <v>211901</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>45726</v>
+      </c>
+      <c r="B47" t="n">
+        <v>4.491000175476074</v>
+      </c>
+      <c r="C47" t="n">
+        <v>4.901000022888184</v>
+      </c>
+      <c r="D47" t="n">
+        <v>4.447000026702881</v>
+      </c>
+      <c r="E47" t="n">
+        <v>4.467000007629395</v>
+      </c>
+      <c r="F47" t="n">
+        <v>221480</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>45727</v>
+      </c>
+      <c r="B48" t="n">
+        <v>4.453000068664551</v>
+      </c>
+      <c r="C48" t="n">
+        <v>4.587999820709229</v>
+      </c>
+      <c r="D48" t="n">
+        <v>4.334000110626221</v>
+      </c>
+      <c r="E48" t="n">
+        <v>4.460999965667725</v>
+      </c>
+      <c r="F48" t="n">
+        <v>192161</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>45728</v>
+      </c>
+      <c r="B49" t="n">
+        <v>4.084000110626221</v>
+      </c>
+      <c r="C49" t="n">
+        <v>4.379000186920166</v>
+      </c>
+      <c r="D49" t="n">
+        <v>4.028999805450439</v>
+      </c>
+      <c r="E49" t="n">
+        <v>4.346000194549561</v>
+      </c>
+      <c r="F49" t="n">
+        <v>224052</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>45729</v>
+      </c>
+      <c r="B50" t="n">
+        <v>4.111000061035156</v>
+      </c>
+      <c r="C50" t="n">
+        <v>4.195000171661377</v>
+      </c>
+      <c r="D50" t="n">
+        <v>3.954999923706055</v>
+      </c>
+      <c r="E50" t="n">
+        <v>4.032000064849854</v>
+      </c>
+      <c r="F50" t="n">
+        <v>227071</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>45730</v>
+      </c>
+      <c r="B51" t="n">
+        <v>4.104000091552734</v>
+      </c>
+      <c r="C51" t="n">
+        <v>4.140999794006348</v>
+      </c>
+      <c r="D51" t="n">
+        <v>3.961999893188477</v>
+      </c>
+      <c r="E51" t="n">
+        <v>4.039999961853027</v>
+      </c>
+      <c r="F51" t="n">
+        <v>144405</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>45733</v>
+      </c>
+      <c r="B52" t="n">
+        <v>4.01800012588501</v>
+      </c>
+      <c r="C52" t="n">
+        <v>4.217999935150146</v>
+      </c>
+      <c r="D52" t="n">
+        <v>3.976999998092651</v>
+      </c>
+      <c r="E52" t="n">
+        <v>4.124000072479248</v>
+      </c>
+      <c r="F52" t="n">
+        <v>153362</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>45734</v>
+      </c>
+      <c r="B53" t="n">
+        <v>4.052000045776367</v>
+      </c>
+      <c r="C53" t="n">
+        <v>4.127999782562256</v>
+      </c>
+      <c r="D53" t="n">
+        <v>3.970000028610229</v>
+      </c>
+      <c r="E53" t="n">
+        <v>4.002999782562256</v>
+      </c>
+      <c r="F53" t="n">
+        <v>171724</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>45735</v>
+      </c>
+      <c r="B54" t="n">
+        <v>4.247000217437744</v>
+      </c>
+      <c r="C54" t="n">
+        <v>4.258999824523926</v>
+      </c>
+      <c r="D54" t="n">
+        <v>4.046000003814697</v>
+      </c>
+      <c r="E54" t="n">
+        <v>4.052000045776367</v>
+      </c>
+      <c r="F54" t="n">
+        <v>149299</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>45736</v>
+      </c>
+      <c r="B55" t="n">
+        <v>3.974999904632568</v>
+      </c>
+      <c r="C55" t="n">
+        <v>4.247000217437744</v>
+      </c>
+      <c r="D55" t="n">
+        <v>3.954999923706055</v>
+      </c>
+      <c r="E55" t="n">
+        <v>4.209000110626221</v>
+      </c>
+      <c r="F55" t="n">
+        <v>185932</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>45737</v>
+      </c>
+      <c r="B56" t="n">
+        <v>3.980000019073486</v>
+      </c>
+      <c r="C56" t="n">
+        <v>4.045000076293945</v>
+      </c>
+      <c r="D56" t="n">
+        <v>3.864000082015991</v>
+      </c>
+      <c r="E56" t="n">
+        <v>3.960999965667725</v>
+      </c>
+      <c r="F56" t="n">
+        <v>125273</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>45740</v>
+      </c>
+      <c r="B57" t="n">
+        <v>3.914000034332275</v>
+      </c>
+      <c r="C57" t="n">
+        <v>4.01200008392334</v>
+      </c>
+      <c r="D57" t="n">
+        <v>3.861999988555908</v>
+      </c>
+      <c r="E57" t="n">
+        <v>3.880000114440918</v>
+      </c>
+      <c r="F57" t="n">
+        <v>78987</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>45741</v>
+      </c>
+      <c r="B58" t="n">
+        <v>3.839999914169312</v>
+      </c>
+      <c r="C58" t="n">
+        <v>3.990000009536743</v>
+      </c>
+      <c r="D58" t="n">
+        <v>3.796000003814697</v>
+      </c>
+      <c r="E58" t="n">
+        <v>3.908999919891357</v>
+      </c>
+      <c r="F58" t="n">
+        <v>50289</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>45742</v>
+      </c>
+      <c r="B59" t="n">
+        <v>3.861000061035156</v>
+      </c>
+      <c r="C59" t="n">
+        <v>3.930000066757202</v>
+      </c>
+      <c r="D59" t="n">
+        <v>3.812999963760376</v>
+      </c>
+      <c r="E59" t="n">
+        <v>3.865999937057495</v>
+      </c>
+      <c r="F59" t="n">
+        <v>52751</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>45743</v>
+      </c>
+      <c r="B60" t="n">
+        <v>3.950000047683716</v>
+      </c>
+      <c r="C60" t="n">
+        <v>4.015999794006348</v>
+      </c>
+      <c r="D60" t="n">
+        <v>3.688999891281128</v>
+      </c>
+      <c r="E60" t="n">
+        <v>3.858999967575073</v>
+      </c>
+      <c r="F60" t="n">
+        <v>181918</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>45744</v>
+      </c>
+      <c r="B61" t="n">
+        <v>4.065000057220459</v>
+      </c>
+      <c r="C61" t="n">
+        <v>4.099999904632568</v>
+      </c>
+      <c r="D61" t="n">
+        <v>3.835999965667725</v>
+      </c>
+      <c r="E61" t="n">
+        <v>3.914999961853027</v>
+      </c>
+      <c r="F61" t="n">
+        <v>176361</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>45747</v>
+      </c>
+      <c r="B62" t="n">
+        <v>4.11899995803833</v>
+      </c>
+      <c r="C62" t="n">
+        <v>4.252999782562256</v>
+      </c>
+      <c r="D62" t="n">
+        <v>4.054999828338623</v>
+      </c>
+      <c r="E62" t="n">
+        <v>4.176000118255615</v>
+      </c>
+      <c r="F62" t="n">
+        <v>171857</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>45748</v>
+      </c>
+      <c r="B63" t="n">
+        <v>3.950999975204468</v>
+      </c>
+      <c r="C63" t="n">
+        <v>4.14799976348877</v>
+      </c>
+      <c r="D63" t="n">
+        <v>3.934000015258789</v>
+      </c>
+      <c r="E63" t="n">
+        <v>4.131999969482422</v>
+      </c>
+      <c r="F63" t="n">
+        <v>156694</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>45749</v>
+      </c>
+      <c r="B64" t="n">
+        <v>4.054999828338623</v>
+      </c>
+      <c r="C64" t="n">
+        <v>4.089000225067139</v>
+      </c>
+      <c r="D64" t="n">
+        <v>3.934999942779541</v>
+      </c>
+      <c r="E64" t="n">
+        <v>3.950000047683716</v>
+      </c>
+      <c r="F64" t="n">
+        <v>141243</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>45750</v>
+      </c>
+      <c r="B65" t="n">
+        <v>4.138000011444092</v>
+      </c>
+      <c r="C65" t="n">
+        <v>4.203000068664551</v>
+      </c>
+      <c r="D65" t="n">
+        <v>3.967999935150146</v>
+      </c>
+      <c r="E65" t="n">
+        <v>4.011000156402588</v>
+      </c>
+      <c r="F65" t="n">
+        <v>165412</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>45751</v>
+      </c>
+      <c r="B66" t="n">
+        <v>3.836999893188477</v>
+      </c>
+      <c r="C66" t="n">
+        <v>4.152999877929688</v>
+      </c>
+      <c r="D66" t="n">
+        <v>3.811000108718872</v>
+      </c>
+      <c r="E66" t="n">
+        <v>4.11899995803833</v>
+      </c>
+      <c r="F66" t="n">
+        <v>246548</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>45754</v>
+      </c>
+      <c r="B67" t="n">
+        <v>3.654999971389771</v>
+      </c>
+      <c r="C67" t="n">
+        <v>3.938999891281128</v>
+      </c>
+      <c r="D67" t="n">
+        <v>3.599999904632568</v>
+      </c>
+      <c r="E67" t="n">
+        <v>3.811000108718872</v>
+      </c>
+      <c r="F67" t="n">
+        <v>298843</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="B68" t="n">
+        <v>3.464999914169312</v>
+      </c>
+      <c r="C68" t="n">
+        <v>3.782999992370605</v>
+      </c>
+      <c r="D68" t="n">
+        <v>3.461999893188477</v>
+      </c>
+      <c r="E68" t="n">
+        <v>3.630000114440918</v>
+      </c>
+      <c r="F68" t="n">
+        <v>278152</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>45756</v>
+      </c>
+      <c r="B69" t="n">
+        <v>3.815999984741211</v>
+      </c>
+      <c r="C69" t="n">
+        <v>3.828999996185303</v>
+      </c>
+      <c r="D69" t="n">
+        <v>3.335999965667725</v>
+      </c>
+      <c r="E69" t="n">
+        <v>3.480999946594238</v>
+      </c>
+      <c r="F69" t="n">
+        <v>359064</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>45757</v>
+      </c>
+      <c r="B70" t="n">
+        <v>3.556999921798706</v>
+      </c>
+      <c r="C70" t="n">
+        <v>3.750999927520752</v>
+      </c>
+      <c r="D70" t="n">
+        <v>3.466000080108643</v>
+      </c>
+      <c r="E70" t="n">
+        <v>3.746999979019165</v>
+      </c>
+      <c r="F70" t="n">
+        <v>260676</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>45758</v>
+      </c>
+      <c r="B71" t="n">
+        <v>3.526999950408936</v>
+      </c>
+      <c r="C71" t="n">
+        <v>3.575999975204468</v>
+      </c>
+      <c r="D71" t="n">
+        <v>3.394000053405762</v>
+      </c>
+      <c r="E71" t="n">
+        <v>3.519999980926514</v>
+      </c>
+      <c r="F71" t="n">
+        <v>181628</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>45761</v>
+      </c>
+      <c r="B72" t="n">
+        <v>3.325000047683716</v>
+      </c>
+      <c r="C72" t="n">
+        <v>3.61299991607666</v>
+      </c>
+      <c r="D72" t="n">
+        <v>3.312000036239624</v>
+      </c>
+      <c r="E72" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F72" t="n">
+        <v>160225</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>45762</v>
+      </c>
+      <c r="B73" t="n">
+        <v>3.328999996185303</v>
+      </c>
+      <c r="C73" t="n">
+        <v>3.378000020980835</v>
+      </c>
+      <c r="D73" t="n">
+        <v>3.216000080108643</v>
+      </c>
+      <c r="E73" t="n">
+        <v>3.345000028610229</v>
+      </c>
+      <c r="F73" t="n">
+        <v>143589</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>45763</v>
+      </c>
+      <c r="B74" t="n">
+        <v>3.246999979019165</v>
+      </c>
+      <c r="C74" t="n">
+        <v>3.318000078201294</v>
+      </c>
+      <c r="D74" t="n">
+        <v>3.203999996185303</v>
+      </c>
+      <c r="E74" t="n">
+        <v>3.318000078201294</v>
+      </c>
+      <c r="F74" t="n">
+        <v>150410</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>45764</v>
+      </c>
+      <c r="B75" t="n">
+        <v>3.244999885559082</v>
+      </c>
+      <c r="C75" t="n">
+        <v>3.334000110626221</v>
+      </c>
+      <c r="D75" t="n">
+        <v>3.190999984741211</v>
+      </c>
+      <c r="E75" t="n">
+        <v>3.26200008392334</v>
+      </c>
+      <c r="F75" t="n">
+        <v>145610</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>45768</v>
+      </c>
+      <c r="B76" t="n">
+        <v>3.016000032424927</v>
+      </c>
+      <c r="C76" t="n">
+        <v>3.224999904632568</v>
+      </c>
+      <c r="D76" t="n">
+        <v>2.99399995803833</v>
+      </c>
+      <c r="E76" t="n">
+        <v>3.197999954223633</v>
+      </c>
+      <c r="F76" t="n">
+        <v>175116</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>45769</v>
+      </c>
+      <c r="B77" t="n">
+        <v>3.006999969482422</v>
+      </c>
+      <c r="C77" t="n">
+        <v>3.095000028610229</v>
+      </c>
+      <c r="D77" t="n">
+        <v>2.954999923706055</v>
+      </c>
+      <c r="E77" t="n">
+        <v>3.051000118255615</v>
+      </c>
+      <c r="F77" t="n">
+        <v>133976</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>45770</v>
+      </c>
+      <c r="B78" t="n">
+        <v>3.022000074386597</v>
+      </c>
+      <c r="C78" t="n">
+        <v>3.073999881744385</v>
+      </c>
+      <c r="D78" t="n">
+        <v>2.967000007629395</v>
+      </c>
+      <c r="E78" t="n">
+        <v>3.046000003814697</v>
+      </c>
+      <c r="F78" t="n">
+        <v>86140</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>45771</v>
+      </c>
+      <c r="B79" t="n">
+        <v>2.930000066757202</v>
+      </c>
+      <c r="C79" t="n">
+        <v>3.016000032424927</v>
+      </c>
+      <c r="D79" t="n">
+        <v>2.858000040054321</v>
+      </c>
+      <c r="E79" t="n">
+        <v>3.010999917984009</v>
+      </c>
+      <c r="F79" t="n">
+        <v>66984</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>45772</v>
+      </c>
+      <c r="B80" t="n">
+        <v>2.937000036239624</v>
+      </c>
+      <c r="C80" t="n">
+        <v>2.983000040054321</v>
+      </c>
+      <c r="D80" t="n">
+        <v>2.868000030517578</v>
+      </c>
+      <c r="E80" t="n">
+        <v>2.938999891281128</v>
+      </c>
+      <c r="F80" t="n">
+        <v>58815</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>45775</v>
+      </c>
+      <c r="B81" t="n">
+        <v>3.170000076293945</v>
+      </c>
+      <c r="C81" t="n">
+        <v>3.187000036239624</v>
+      </c>
+      <c r="D81" t="n">
+        <v>2.858999967575073</v>
+      </c>
+      <c r="E81" t="n">
+        <v>2.884000062942505</v>
+      </c>
+      <c r="F81" t="n">
+        <v>229473</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>45776</v>
+      </c>
+      <c r="B82" t="n">
+        <v>3.385999917984009</v>
+      </c>
+      <c r="C82" t="n">
+        <v>3.457000017166138</v>
+      </c>
+      <c r="D82" t="n">
+        <v>3.306999921798706</v>
+      </c>
+      <c r="E82" t="n">
+        <v>3.319999933242798</v>
+      </c>
+      <c r="F82" t="n">
+        <v>156565</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>45777</v>
+      </c>
+      <c r="B83" t="n">
+        <v>3.325999975204468</v>
+      </c>
+      <c r="C83" t="n">
+        <v>3.398999929428101</v>
+      </c>
+      <c r="D83" t="n">
+        <v>3.259999990463257</v>
+      </c>
+      <c r="E83" t="n">
+        <v>3.380000114440918</v>
+      </c>
+      <c r="F83" t="n">
+        <v>145962</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>45778</v>
+      </c>
+      <c r="B84" t="n">
+        <v>3.479000091552734</v>
+      </c>
+      <c r="C84" t="n">
+        <v>3.539999961853027</v>
+      </c>
+      <c r="D84" t="n">
+        <v>3.339999914169312</v>
+      </c>
+      <c r="E84" t="n">
+        <v>3.352999925613403</v>
+      </c>
+      <c r="F84" t="n">
+        <v>159640</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>45779</v>
+      </c>
+      <c r="B85" t="n">
+        <v>3.630000114440918</v>
+      </c>
+      <c r="C85" t="n">
+        <v>3.67300009727478</v>
+      </c>
+      <c r="D85" t="n">
+        <v>3.417999982833862</v>
+      </c>
+      <c r="E85" t="n">
+        <v>3.446000099182129</v>
+      </c>
+      <c r="F85" t="n">
+        <v>140954</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>45782</v>
+      </c>
+      <c r="B86" t="n">
+        <v>3.549999952316284</v>
+      </c>
+      <c r="C86" t="n">
+        <v>3.746999979019165</v>
+      </c>
+      <c r="D86" t="n">
+        <v>3.530999898910522</v>
+      </c>
+      <c r="E86" t="n">
+        <v>3.671000003814697</v>
+      </c>
+      <c r="F86" t="n">
+        <v>161317</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>45783</v>
+      </c>
+      <c r="B87" t="n">
+        <v>3.463000059127808</v>
+      </c>
+      <c r="C87" t="n">
+        <v>3.648000001907349</v>
+      </c>
+      <c r="D87" t="n">
+        <v>3.42300009727478</v>
+      </c>
+      <c r="E87" t="n">
+        <v>3.568000078201294</v>
+      </c>
+      <c r="F87" t="n">
+        <v>200855</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>45784</v>
+      </c>
+      <c r="B88" t="n">
+        <v>3.621000051498413</v>
+      </c>
+      <c r="C88" t="n">
+        <v>3.655999898910522</v>
+      </c>
+      <c r="D88" t="n">
+        <v>3.486999988555908</v>
+      </c>
+      <c r="E88" t="n">
+        <v>3.486999988555908</v>
+      </c>
+      <c r="F88" t="n">
+        <v>162366</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>45785</v>
+      </c>
+      <c r="B89" t="n">
+        <v>3.592000007629395</v>
+      </c>
+      <c r="C89" t="n">
+        <v>3.723000049591064</v>
+      </c>
+      <c r="D89" t="n">
+        <v>3.526999950408936</v>
+      </c>
+      <c r="E89" t="n">
+        <v>3.631999969482422</v>
+      </c>
+      <c r="F89" t="n">
+        <v>158746</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>45786</v>
+      </c>
+      <c r="B90" t="n">
+        <v>3.795000076293945</v>
+      </c>
+      <c r="C90" t="n">
+        <v>3.815000057220459</v>
+      </c>
+      <c r="D90" t="n">
+        <v>3.61299991607666</v>
+      </c>
+      <c r="E90" t="n">
+        <v>3.621000051498413</v>
+      </c>
+      <c r="F90" t="n">
+        <v>174974</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>45789</v>
+      </c>
+      <c r="B91" t="n">
+        <v>3.645999908447266</v>
+      </c>
+      <c r="C91" t="n">
+        <v>3.839999914169312</v>
+      </c>
+      <c r="D91" t="n">
+        <v>3.608000040054321</v>
+      </c>
+      <c r="E91" t="n">
+        <v>3.775000095367432</v>
+      </c>
+      <c r="F91" t="n">
+        <v>163731</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>45790</v>
+      </c>
+      <c r="B92" t="n">
+        <v>3.647000074386597</v>
+      </c>
+      <c r="C92" t="n">
+        <v>3.727999925613403</v>
+      </c>
+      <c r="D92" t="n">
+        <v>3.569999933242798</v>
+      </c>
+      <c r="E92" t="n">
+        <v>3.677000045776367</v>
+      </c>
+      <c r="F92" t="n">
+        <v>130015</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>45791</v>
+      </c>
+      <c r="B93" t="n">
+        <v>3.492000102996826</v>
+      </c>
+      <c r="C93" t="n">
+        <v>3.634999990463257</v>
+      </c>
+      <c r="D93" t="n">
+        <v>3.453999996185303</v>
+      </c>
+      <c r="E93" t="n">
+        <v>3.621999979019165</v>
+      </c>
+      <c r="F93" t="n">
+        <v>119947</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>45792</v>
+      </c>
+      <c r="B94" t="n">
+        <v>3.361999988555908</v>
+      </c>
+      <c r="C94" t="n">
+        <v>3.499000072479248</v>
+      </c>
+      <c r="D94" t="n">
+        <v>3.335000038146973</v>
+      </c>
+      <c r="E94" t="n">
+        <v>3.467000007629395</v>
+      </c>
+      <c r="F94" t="n">
+        <v>152653</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n">
+        <v>45793</v>
+      </c>
+      <c r="B95" t="n">
+        <v>3.334000110626221</v>
+      </c>
+      <c r="C95" t="n">
+        <v>3.448999881744385</v>
+      </c>
+      <c r="D95" t="n">
+        <v>3.305000066757202</v>
+      </c>
+      <c r="E95" t="n">
+        <v>3.371999979019165</v>
+      </c>
+      <c r="F95" t="n">
+        <v>141334</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n">
+        <v>45796</v>
+      </c>
+      <c r="B96" t="n">
+        <v>3.11299991607666</v>
+      </c>
+      <c r="C96" t="n">
+        <v>3.269999980926514</v>
+      </c>
+      <c r="D96" t="n">
+        <v>3.098000049591064</v>
+      </c>
+      <c r="E96" t="n">
+        <v>3.269000053405762</v>
+      </c>
+      <c r="F96" t="n">
+        <v>182905</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n">
+        <v>45797</v>
+      </c>
+      <c r="B97" t="n">
+        <v>3.427000045776367</v>
+      </c>
+      <c r="C97" t="n">
+        <v>3.453000068664551</v>
+      </c>
+      <c r="D97" t="n">
+        <v>3.107000112533569</v>
+      </c>
+      <c r="E97" t="n">
+        <v>3.107000112533569</v>
+      </c>
+      <c r="F97" t="n">
+        <v>230771</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>45798</v>
+      </c>
+      <c r="B98" t="n">
+        <v>3.368000030517578</v>
+      </c>
+      <c r="C98" t="n">
+        <v>3.513000011444092</v>
+      </c>
+      <c r="D98" t="n">
+        <v>3.335999965667725</v>
+      </c>
+      <c r="E98" t="n">
+        <v>3.414999961853027</v>
+      </c>
+      <c r="F98" t="n">
+        <v>135733</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n">
+        <v>45799</v>
+      </c>
+      <c r="B99" t="n">
+        <v>3.253000020980835</v>
+      </c>
+      <c r="C99" t="n">
+        <v>3.38100004196167</v>
+      </c>
+      <c r="D99" t="n">
+        <v>3.23799991607666</v>
+      </c>
+      <c r="E99" t="n">
+        <v>3.355999946594238</v>
+      </c>
+      <c r="F99" t="n">
+        <v>91988</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>45800</v>
+      </c>
+      <c r="B100" t="n">
+        <v>3.334000110626221</v>
+      </c>
+      <c r="C100" t="n">
+        <v>3.349999904632568</v>
+      </c>
+      <c r="D100" t="n">
+        <v>3.217000007629395</v>
+      </c>
+      <c r="E100" t="n">
+        <v>3.282999992370605</v>
+      </c>
+      <c r="F100" t="n">
+        <v>60597</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="n">
+        <v>45804</v>
+      </c>
+      <c r="B101" t="n">
+        <v>3.398000001907349</v>
+      </c>
+      <c r="C101" t="n">
+        <v>3.444999933242798</v>
+      </c>
+      <c r="D101" t="n">
+        <v>3.21399998664856</v>
+      </c>
+      <c r="E101" t="n">
+        <v>3.375999927520752</v>
+      </c>
+      <c r="F101" t="n">
+        <v>55895</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>45805</v>
+      </c>
+      <c r="B102" t="n">
+        <v>3.203999996185303</v>
+      </c>
+      <c r="C102" t="n">
+        <v>3.510999917984009</v>
+      </c>
+      <c r="D102" t="n">
+        <v>3.151999950408936</v>
+      </c>
+      <c r="E102" t="n">
+        <v>3.404999971389771</v>
+      </c>
+      <c r="F102" t="n">
+        <v>204259</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>45806</v>
+      </c>
+      <c r="B103" t="n">
+        <v>3.522000074386597</v>
+      </c>
+      <c r="C103" t="n">
+        <v>3.575999975204468</v>
+      </c>
+      <c r="D103" t="n">
+        <v>3.437000036239624</v>
+      </c>
+      <c r="E103" t="n">
+        <v>3.535000085830688</v>
+      </c>
+      <c r="F103" t="n">
+        <v>180662</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>45807</v>
+      </c>
+      <c r="B104" t="n">
+        <v>3.447000026702881</v>
+      </c>
+      <c r="C104" t="n">
+        <v>3.563999891281128</v>
+      </c>
+      <c r="D104" t="n">
+        <v>3.440000057220459</v>
+      </c>
+      <c r="E104" t="n">
+        <v>3.535000085830688</v>
+      </c>
+      <c r="F104" t="n">
+        <v>131545</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>45810</v>
+      </c>
+      <c r="B105" t="n">
+        <v>3.694000005722046</v>
+      </c>
+      <c r="C105" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D105" t="n">
+        <v>3.500999927520752</v>
+      </c>
+      <c r="E105" t="n">
+        <v>3.500999927520752</v>
+      </c>
+      <c r="F105" t="n">
+        <v>199977</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>45811</v>
+      </c>
+      <c r="B106" t="n">
+        <v>3.721999883651733</v>
+      </c>
+      <c r="C106" t="n">
+        <v>3.763999938964844</v>
+      </c>
+      <c r="D106" t="n">
+        <v>3.630000114440918</v>
+      </c>
+      <c r="E106" t="n">
+        <v>3.747999906539917</v>
+      </c>
+      <c r="F106" t="n">
+        <v>139410</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>45812</v>
+      </c>
+      <c r="B107" t="n">
+        <v>3.716000080108643</v>
+      </c>
+      <c r="C107" t="n">
+        <v>3.740000009536743</v>
+      </c>
+      <c r="D107" t="n">
+        <v>3.66100001335144</v>
+      </c>
+      <c r="E107" t="n">
+        <v>3.729000091552734</v>
+      </c>
+      <c r="F107" t="n">
+        <v>126093</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>45813</v>
+      </c>
+      <c r="B108" t="n">
+        <v>3.677000045776367</v>
+      </c>
+      <c r="C108" t="n">
+        <v>3.790999889373779</v>
+      </c>
+      <c r="D108" t="n">
+        <v>3.619999885559082</v>
+      </c>
+      <c r="E108" t="n">
+        <v>3.703000068664551</v>
+      </c>
+      <c r="F108" t="n">
+        <v>208764</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>45814</v>
+      </c>
+      <c r="B109" t="n">
+        <v>3.783999919891357</v>
+      </c>
+      <c r="C109" t="n">
+        <v>3.816999912261963</v>
+      </c>
+      <c r="D109" t="n">
+        <v>3.648999929428101</v>
+      </c>
+      <c r="E109" t="n">
+        <v>3.653000116348267</v>
+      </c>
+      <c r="F109" t="n">
+        <v>180631</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>45817</v>
+      </c>
+      <c r="B110" t="n">
+        <v>3.634999990463257</v>
+      </c>
+      <c r="C110" t="n">
+        <v>3.769000053405762</v>
+      </c>
+      <c r="D110" t="n">
+        <v>3.581000089645386</v>
+      </c>
+      <c r="E110" t="n">
+        <v>3.719000101089478</v>
+      </c>
+      <c r="F110" t="n">
+        <v>215678</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n">
+        <v>45818</v>
+      </c>
+      <c r="B111" t="n">
+        <v>3.532999992370605</v>
+      </c>
+      <c r="C111" t="n">
+        <v>3.661999940872192</v>
+      </c>
+      <c r="D111" t="n">
+        <v>3.515000104904175</v>
+      </c>
+      <c r="E111" t="n">
+        <v>3.611999988555908</v>
+      </c>
+      <c r="F111" t="n">
+        <v>179312</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n">
+        <v>45819</v>
+      </c>
+      <c r="B112" t="n">
+        <v>3.506999969482422</v>
+      </c>
+      <c r="C112" t="n">
+        <v>3.625999927520752</v>
+      </c>
+      <c r="D112" t="n">
+        <v>3.453000068664551</v>
+      </c>
+      <c r="E112" t="n">
+        <v>3.526000022888184</v>
+      </c>
+      <c r="F112" t="n">
+        <v>211742</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n">
+        <v>45820</v>
+      </c>
+      <c r="B113" t="n">
+        <v>3.492000102996826</v>
+      </c>
+      <c r="C113" t="n">
+        <v>3.644000053405762</v>
+      </c>
+      <c r="D113" t="n">
+        <v>3.466000080108643</v>
+      </c>
+      <c r="E113" t="n">
+        <v>3.519000053405762</v>
+      </c>
+      <c r="F113" t="n">
+        <v>220853</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n">
+        <v>45821</v>
+      </c>
+      <c r="B114" t="n">
+        <v>3.581000089645386</v>
+      </c>
+      <c r="C114" t="n">
+        <v>3.622999906539917</v>
+      </c>
+      <c r="D114" t="n">
+        <v>3.499000072479248</v>
+      </c>
+      <c r="E114" t="n">
+        <v>3.540999889373779</v>
+      </c>
+      <c r="F114" t="n">
+        <v>133290</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>45824</v>
+      </c>
+      <c r="B115" t="n">
+        <v>3.747999906539917</v>
+      </c>
+      <c r="C115" t="n">
+        <v>3.759999990463257</v>
+      </c>
+      <c r="D115" t="n">
+        <v>3.634000062942505</v>
+      </c>
+      <c r="E115" t="n">
+        <v>3.703999996185303</v>
+      </c>
+      <c r="F115" t="n">
+        <v>171746</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>45825</v>
+      </c>
+      <c r="B116" t="n">
+        <v>3.851000070571899</v>
+      </c>
+      <c r="C116" t="n">
+        <v>3.88100004196167</v>
+      </c>
+      <c r="D116" t="n">
+        <v>3.720000028610229</v>
+      </c>
+      <c r="E116" t="n">
+        <v>3.746000051498413</v>
+      </c>
+      <c r="F116" t="n">
+        <v>163883</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>45826</v>
+      </c>
+      <c r="B117" t="n">
+        <v>3.989000082015991</v>
+      </c>
+      <c r="C117" t="n">
+        <v>4.001999855041504</v>
+      </c>
+      <c r="D117" t="n">
+        <v>3.813999891281128</v>
+      </c>
+      <c r="E117" t="n">
+        <v>3.861999988555908</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>45828</v>
+      </c>
+      <c r="B118" t="n">
+        <v>3.846999883651733</v>
+      </c>
+      <c r="C118" t="n">
+        <v>4.14799976348877</v>
+      </c>
+      <c r="D118" t="n">
+        <v>3.818000078201294</v>
+      </c>
+      <c r="E118" t="n">
+        <v>3.984999895095825</v>
+      </c>
+      <c r="F118" t="n">
+        <v>194501</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>45831</v>
+      </c>
+      <c r="B119" t="n">
+        <v>3.697999954223633</v>
+      </c>
+      <c r="C119" t="n">
+        <v>3.948999881744385</v>
+      </c>
+      <c r="D119" t="n">
+        <v>3.665999889373779</v>
+      </c>
+      <c r="E119" t="n">
+        <v>3.948999881744385</v>
+      </c>
+      <c r="F119" t="n">
+        <v>102698</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>45832</v>
+      </c>
+      <c r="B120" t="n">
+        <v>3.536999940872192</v>
+      </c>
+      <c r="C120" t="n">
+        <v>3.684000015258789</v>
+      </c>
+      <c r="D120" t="n">
+        <v>3.529999971389771</v>
+      </c>
+      <c r="E120" t="n">
+        <v>3.680999994277954</v>
+      </c>
+      <c r="F120" t="n">
+        <v>70983</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>45833</v>
+      </c>
+      <c r="B121" t="n">
+        <v>3.405999898910522</v>
+      </c>
+      <c r="C121" t="n">
+        <v>3.586999893188477</v>
+      </c>
+      <c r="D121" t="n">
+        <v>3.371999979019165</v>
+      </c>
+      <c r="E121" t="n">
+        <v>3.549000024795532</v>
+      </c>
+      <c r="F121" t="n">
+        <v>74500</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>45834</v>
+      </c>
+      <c r="B122" t="n">
+        <v>3.260999917984009</v>
+      </c>
+      <c r="C122" t="n">
+        <v>3.424999952316284</v>
+      </c>
+      <c r="D122" t="n">
+        <v>3.198999881744385</v>
+      </c>
+      <c r="E122" t="n">
+        <v>3.394000053405762</v>
+      </c>
+      <c r="F122" t="n">
+        <v>230496</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>45835</v>
+      </c>
+      <c r="B123" t="n">
+        <v>3.739000082015991</v>
+      </c>
+      <c r="C123" t="n">
+        <v>3.750999927520752</v>
+      </c>
+      <c r="D123" t="n">
+        <v>3.513000011444092</v>
+      </c>
+      <c r="E123" t="n">
+        <v>3.529999971389771</v>
+      </c>
+      <c r="F123" t="n">
+        <v>153056</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>45838</v>
+      </c>
+      <c r="B124" t="n">
+        <v>3.456000089645386</v>
+      </c>
+      <c r="C124" t="n">
+        <v>3.73799991607666</v>
+      </c>
+      <c r="D124" t="n">
+        <v>3.421000003814697</v>
+      </c>
+      <c r="E124" t="n">
+        <v>3.734999895095825</v>
+      </c>
+      <c r="F124" t="n">
+        <v>212922</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>45839</v>
+      </c>
+      <c r="B125" t="n">
+        <v>3.414999961853027</v>
+      </c>
+      <c r="C125" t="n">
+        <v>3.467999935150146</v>
+      </c>
+      <c r="D125" t="n">
+        <v>3.292999982833862</v>
+      </c>
+      <c r="E125" t="n">
+        <v>3.453000068664551</v>
+      </c>
+      <c r="F125" t="n">
+        <v>177010</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>45840</v>
+      </c>
+      <c r="B126" t="n">
+        <v>3.48799991607666</v>
+      </c>
+      <c r="C126" t="n">
+        <v>3.519999980926514</v>
+      </c>
+      <c r="D126" t="n">
+        <v>3.365999937057495</v>
+      </c>
+      <c r="E126" t="n">
+        <v>3.41700005531311</v>
+      </c>
+      <c r="F126" t="n">
+        <v>115605</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>45841</v>
+      </c>
+      <c r="B127" t="n">
+        <v>3.408999919891357</v>
+      </c>
+      <c r="C127" t="n">
+        <v>3.573999881744385</v>
+      </c>
+      <c r="D127" t="n">
+        <v>3.391999959945679</v>
+      </c>
+      <c r="E127" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>45842</v>
+      </c>
+      <c r="B128" t="n">
+        <v>3.38700008392334</v>
+      </c>
+      <c r="C128" t="n">
+        <v>3.434999942779541</v>
+      </c>
+      <c r="D128" t="n">
+        <v>3.365999937057495</v>
+      </c>
+      <c r="E128" t="n">
+        <v>3.403000116348267</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>45845</v>
+      </c>
+      <c r="B129" t="n">
+        <v>3.411999940872192</v>
+      </c>
+      <c r="C129" t="n">
+        <v>3.471999883651733</v>
+      </c>
+      <c r="D129" t="n">
+        <v>3.275000095367432</v>
+      </c>
+      <c r="E129" t="n">
+        <v>3.344000101089478</v>
+      </c>
+      <c r="F129" t="n">
+        <v>163396</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>45846</v>
+      </c>
+      <c r="B130" t="n">
+        <v>3.339999914169312</v>
+      </c>
+      <c r="C130" t="n">
+        <v>3.469000101089478</v>
+      </c>
+      <c r="D130" t="n">
+        <v>3.325000047683716</v>
+      </c>
+      <c r="E130" t="n">
+        <v>3.405999898910522</v>
+      </c>
+      <c r="F130" t="n">
+        <v>130237</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>45847</v>
+      </c>
+      <c r="B131" t="n">
+        <v>3.21399998664856</v>
+      </c>
+      <c r="C131" t="n">
+        <v>3.358999967575073</v>
+      </c>
+      <c r="D131" t="n">
+        <v>3.148999929428101</v>
+      </c>
+      <c r="E131" t="n">
+        <v>3.348000049591064</v>
+      </c>
+      <c r="F131" t="n">
+        <v>217203</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>45848</v>
+      </c>
+      <c r="B132" t="n">
+        <v>3.336999893188477</v>
+      </c>
+      <c r="C132" t="n">
+        <v>3.398000001907349</v>
+      </c>
+      <c r="D132" t="n">
+        <v>3.190999984741211</v>
+      </c>
+      <c r="E132" t="n">
+        <v>3.20799994468689</v>
+      </c>
+      <c r="F132" t="n">
+        <v>163043</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>45849</v>
+      </c>
+      <c r="B133" t="n">
+        <v>3.313999891281128</v>
+      </c>
+      <c r="C133" t="n">
+        <v>3.417999982833862</v>
+      </c>
+      <c r="D133" t="n">
+        <v>3.292999982833862</v>
+      </c>
+      <c r="E133" t="n">
+        <v>3.365000009536743</v>
+      </c>
+      <c r="F133" t="n">
+        <v>130290</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>45852</v>
+      </c>
+      <c r="B134" t="n">
+        <v>3.466000080108643</v>
+      </c>
+      <c r="C134" t="n">
+        <v>3.499000072479248</v>
+      </c>
+      <c r="D134" t="n">
+        <v>3.382999897003174</v>
+      </c>
+      <c r="E134" t="n">
+        <v>3.404000043869019</v>
+      </c>
+      <c r="F134" t="n">
+        <v>149455</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>45853</v>
+      </c>
+      <c r="B135" t="n">
+        <v>3.523000001907349</v>
+      </c>
+      <c r="C135" t="n">
+        <v>3.54200005531311</v>
+      </c>
+      <c r="D135" t="n">
+        <v>3.401000022888184</v>
+      </c>
+      <c r="E135" t="n">
+        <v>3.447000026702881</v>
+      </c>
+      <c r="F135" t="n">
+        <v>132955</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>45854</v>
+      </c>
+      <c r="B136" t="n">
+        <v>3.551000118255615</v>
+      </c>
+      <c r="C136" t="n">
+        <v>3.598000049591064</v>
+      </c>
+      <c r="D136" t="n">
+        <v>3.490999937057495</v>
+      </c>
+      <c r="E136" t="n">
+        <v>3.519000053405762</v>
+      </c>
+      <c r="F136" t="n">
+        <v>116044</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>45855</v>
+      </c>
+      <c r="B137" t="n">
+        <v>3.54200005531311</v>
+      </c>
+      <c r="C137" t="n">
+        <v>3.628999948501587</v>
+      </c>
+      <c r="D137" t="n">
+        <v>3.510999917984009</v>
+      </c>
+      <c r="E137" t="n">
+        <v>3.556999921798706</v>
+      </c>
+      <c r="F137" t="n">
+        <v>108569</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>45856</v>
+      </c>
+      <c r="B138" t="n">
+        <v>3.565000057220459</v>
+      </c>
+      <c r="C138" t="n">
+        <v>3.628000020980835</v>
+      </c>
+      <c r="D138" t="n">
+        <v>3.49399995803833</v>
+      </c>
+      <c r="E138" t="n">
+        <v>3.519000053405762</v>
+      </c>
+      <c r="F138" t="n">
+        <v>123961</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>45859</v>
+      </c>
+      <c r="B139" t="n">
+        <v>3.325000047683716</v>
+      </c>
+      <c r="C139" t="n">
+        <v>3.474999904632568</v>
+      </c>
+      <c r="D139" t="n">
+        <v>3.286999940872192</v>
+      </c>
+      <c r="E139" t="n">
+        <v>3.46399998664856</v>
+      </c>
+      <c r="F139" t="n">
+        <v>176972</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>45860</v>
+      </c>
+      <c r="B140" t="n">
+        <v>3.252000093460083</v>
+      </c>
+      <c r="C140" t="n">
+        <v>3.331000089645386</v>
+      </c>
+      <c r="D140" t="n">
+        <v>3.210000038146973</v>
+      </c>
+      <c r="E140" t="n">
+        <v>3.316999912261963</v>
+      </c>
+      <c r="F140" t="n">
+        <v>124612</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>45861</v>
+      </c>
+      <c r="B141" t="n">
+        <v>3.07699990272522</v>
+      </c>
+      <c r="C141" t="n">
+        <v>3.266999959945679</v>
+      </c>
+      <c r="D141" t="n">
+        <v>3.061000108718872</v>
+      </c>
+      <c r="E141" t="n">
+        <v>3.253000020980835</v>
+      </c>
+      <c r="F141" t="n">
+        <v>158442</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>45862</v>
+      </c>
+      <c r="B142" t="n">
+        <v>3.094000101089478</v>
+      </c>
+      <c r="C142" t="n">
+        <v>3.165999889373779</v>
+      </c>
+      <c r="D142" t="n">
+        <v>3.065000057220459</v>
+      </c>
+      <c r="E142" t="n">
+        <v>3.069999933242798</v>
+      </c>
+      <c r="F142" t="n">
+        <v>75361</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>45863</v>
+      </c>
+      <c r="B143" t="n">
+        <v>3.109999895095825</v>
+      </c>
+      <c r="C143" t="n">
+        <v>3.144999980926514</v>
+      </c>
+      <c r="D143" t="n">
+        <v>3.068000078201294</v>
+      </c>
+      <c r="E143" t="n">
+        <v>3.109999895095825</v>
+      </c>
+      <c r="F143" t="n">
+        <v>39115</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="n">
+        <v>45866</v>
+      </c>
+      <c r="B144" t="n">
+        <v>2.98799991607666</v>
+      </c>
+      <c r="C144" t="n">
+        <v>3.140000104904175</v>
+      </c>
+      <c r="D144" t="n">
+        <v>2.983999967575073</v>
+      </c>
+      <c r="E144" t="n">
+        <v>3.092999935150146</v>
+      </c>
+      <c r="F144" t="n">
+        <v>69852</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="n">
+        <v>45867</v>
+      </c>
+      <c r="B145" t="n">
+        <v>3.081000089645386</v>
+      </c>
+      <c r="C145" t="n">
+        <v>3.111999988555908</v>
+      </c>
+      <c r="D145" t="n">
+        <v>3.010999917984009</v>
+      </c>
+      <c r="E145" t="n">
+        <v>3.033999919891357</v>
+      </c>
+      <c r="F145" t="n">
+        <v>117204</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="n">
+        <v>45868</v>
+      </c>
+      <c r="B146" t="n">
+        <v>3.045000076293945</v>
+      </c>
+      <c r="C146" t="n">
+        <v>3.186000108718872</v>
+      </c>
+      <c r="D146" t="n">
+        <v>3.013999938964844</v>
+      </c>
+      <c r="E146" t="n">
+        <v>3.164000034332275</v>
+      </c>
+      <c r="F146" t="n">
+        <v>126252</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="n">
+        <v>45869</v>
+      </c>
+      <c r="B147" t="n">
+        <v>3.105999946594238</v>
+      </c>
+      <c r="C147" t="n">
+        <v>3.114000082015991</v>
+      </c>
+      <c r="D147" t="n">
+        <v>2.971999883651733</v>
+      </c>
+      <c r="E147" t="n">
+        <v>3.026000022888184</v>
+      </c>
+      <c r="F147" t="n">
+        <v>168396</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="B148" t="n">
+        <v>3.08299994468689</v>
+      </c>
+      <c r="C148" t="n">
+        <v>3.13100004196167</v>
+      </c>
+      <c r="D148" t="n">
+        <v>3.051000118255615</v>
+      </c>
+      <c r="E148" t="n">
+        <v>3.099999904632568</v>
+      </c>
+      <c r="F148" t="n">
+        <v>102378</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="n">
+        <v>45873</v>
+      </c>
+      <c r="B149" t="n">
+        <v>2.931999921798706</v>
+      </c>
+      <c r="C149" t="n">
+        <v>3.078000068664551</v>
+      </c>
+      <c r="D149" t="n">
+        <v>2.894999980926514</v>
+      </c>
+      <c r="E149" t="n">
+        <v>3.065000057220459</v>
+      </c>
+      <c r="F149" t="n">
+        <v>167435</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="n">
+        <v>45874</v>
+      </c>
+      <c r="B150" t="n">
+        <v>3.009999990463257</v>
+      </c>
+      <c r="C150" t="n">
+        <v>3.040999889373779</v>
+      </c>
+      <c r="D150" t="n">
+        <v>2.928999900817871</v>
+      </c>
+      <c r="E150" t="n">
+        <v>2.946000099182129</v>
+      </c>
+      <c r="F150" t="n">
+        <v>134125</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="n">
+        <v>45875</v>
+      </c>
+      <c r="B151" t="n">
+        <v>3.07699990272522</v>
+      </c>
+      <c r="C151" t="n">
+        <v>3.095999956130981</v>
+      </c>
+      <c r="D151" t="n">
+        <v>2.944999933242798</v>
+      </c>
+      <c r="E151" t="n">
+        <v>3.015000104904175</v>
+      </c>
+      <c r="F151" t="n">
+        <v>133710</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="n">
+        <v>45876</v>
+      </c>
+      <c r="B152" t="n">
+        <v>3.066999912261963</v>
+      </c>
+      <c r="C152" t="n">
+        <v>3.148000001907349</v>
+      </c>
+      <c r="D152" t="n">
+        <v>3.035000085830688</v>
+      </c>
+      <c r="E152" t="n">
+        <v>3.098999977111816</v>
+      </c>
+      <c r="F152" t="n">
+        <v>171662</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="n">
+        <v>45877</v>
+      </c>
+      <c r="B153" t="n">
+        <v>2.990000009536743</v>
+      </c>
+      <c r="C153" t="n">
+        <v>3.105999946594238</v>
+      </c>
+      <c r="D153" t="n">
+        <v>2.960000038146973</v>
+      </c>
+      <c r="E153" t="n">
+        <v>3.085999965667725</v>
+      </c>
+      <c r="F153" t="n">
+        <v>164260</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="n">
+        <v>45880</v>
+      </c>
+      <c r="B154" t="n">
+        <v>2.953999996185303</v>
+      </c>
+      <c r="C154" t="n">
+        <v>3</v>
+      </c>
+      <c r="D154" t="n">
+        <v>2.88100004196167</v>
+      </c>
+      <c r="E154" t="n">
+        <v>2.894999980926514</v>
+      </c>
+      <c r="F154" t="n">
+        <v>156872</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="n">
+        <v>45881</v>
+      </c>
+      <c r="B155" t="n">
+        <v>2.808000087738037</v>
+      </c>
+      <c r="C155" t="n">
+        <v>2.984999895095825</v>
+      </c>
+      <c r="D155" t="n">
+        <v>2.773999929428101</v>
+      </c>
+      <c r="E155" t="n">
+        <v>2.977999925613403</v>
+      </c>
+      <c r="F155" t="n">
+        <v>219061</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="n">
+        <v>45882</v>
+      </c>
+      <c r="B156" t="n">
+        <v>2.828000068664551</v>
+      </c>
+      <c r="C156" t="n">
+        <v>2.851000070571899</v>
+      </c>
+      <c r="D156" t="n">
+        <v>2.763999938964844</v>
+      </c>
+      <c r="E156" t="n">
+        <v>2.783999919891357</v>
+      </c>
+      <c r="F156" t="n">
+        <v>179251</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="n">
+        <v>45883</v>
+      </c>
+      <c r="B157" t="n">
+        <v>2.841000080108643</v>
+      </c>
+      <c r="C157" t="n">
+        <v>2.851999998092651</v>
+      </c>
+      <c r="D157" t="n">
+        <v>2.773999929428101</v>
+      </c>
+      <c r="E157" t="n">
+        <v>2.818000078201294</v>
+      </c>
+      <c r="F157" t="n">
+        <v>138654</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="n">
+        <v>45884</v>
+      </c>
+      <c r="B158" t="n">
+        <v>2.915999889373779</v>
+      </c>
+      <c r="C158" t="n">
+        <v>2.966000080108643</v>
+      </c>
+      <c r="D158" t="n">
+        <v>2.835999965667725</v>
+      </c>
+      <c r="E158" t="n">
+        <v>2.849999904632568</v>
+      </c>
+      <c r="F158" t="n">
+        <v>132775</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="n">
+        <v>45887</v>
+      </c>
+      <c r="B159" t="n">
+        <v>2.890000104904175</v>
+      </c>
+      <c r="C159" t="n">
+        <v>2.921999931335449</v>
+      </c>
+      <c r="D159" t="n">
+        <v>2.799000024795532</v>
+      </c>
+      <c r="E159" t="n">
+        <v>2.877000093460083</v>
+      </c>
+      <c r="F159" t="n">
+        <v>143784</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="n">
+        <v>45888</v>
+      </c>
+      <c r="B160" t="n">
+        <v>2.766000032424927</v>
+      </c>
+      <c r="C160" t="n">
+        <v>2.911999940872192</v>
+      </c>
+      <c r="D160" t="n">
+        <v>2.724999904632568</v>
+      </c>
+      <c r="E160" t="n">
+        <v>2.904999971389771</v>
+      </c>
+      <c r="F160" t="n">
+        <v>171271</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="n">
+        <v>45889</v>
+      </c>
+      <c r="B161" t="n">
+        <v>2.752000093460083</v>
+      </c>
+      <c r="C161" t="n">
+        <v>2.776999950408936</v>
+      </c>
+      <c r="D161" t="n">
+        <v>2.724999904632568</v>
+      </c>
+      <c r="E161" t="n">
+        <v>2.756999969482422</v>
+      </c>
+      <c r="F161" t="n">
+        <v>121113</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="n">
+        <v>45890</v>
+      </c>
+      <c r="B162" t="n">
+        <v>2.825999975204468</v>
+      </c>
+      <c r="C162" t="n">
+        <v>2.848999977111816</v>
+      </c>
+      <c r="D162" t="n">
+        <v>2.740000009536743</v>
+      </c>
+      <c r="E162" t="n">
+        <v>2.765000104904175</v>
+      </c>
+      <c r="F162" t="n">
+        <v>115270</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="n">
+        <v>45891</v>
+      </c>
+      <c r="B163" t="n">
+        <v>2.697999954223633</v>
+      </c>
+      <c r="C163" t="n">
+        <v>2.819000005722046</v>
+      </c>
+      <c r="D163" t="n">
+        <v>2.688999891281128</v>
+      </c>
+      <c r="E163" t="n">
+        <v>2.812999963760376</v>
+      </c>
+      <c r="F163" t="n">
+        <v>79364</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="n">
+        <v>45894</v>
+      </c>
+      <c r="B164" t="n">
+        <v>2.696000099182129</v>
+      </c>
+      <c r="C164" t="n">
+        <v>2.717000007629395</v>
+      </c>
+      <c r="D164" t="n">
+        <v>2.621999979019165</v>
+      </c>
+      <c r="E164" t="n">
+        <v>2.638999938964844</v>
+      </c>
+      <c r="F164" t="n">
+        <v>60316</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="n">
+        <v>45895</v>
+      </c>
+      <c r="B165" t="n">
+        <v>2.717000007629395</v>
+      </c>
+      <c r="C165" t="n">
+        <v>2.742000102996826</v>
+      </c>
+      <c r="D165" t="n">
+        <v>2.654000043869019</v>
+      </c>
+      <c r="E165" t="n">
+        <v>2.710999965667725</v>
+      </c>
+      <c r="F165" t="n">
+        <v>70243</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="n">
+        <v>45896</v>
+      </c>
+      <c r="B166" t="n">
+        <v>2.867000102996826</v>
+      </c>
+      <c r="C166" t="n">
+        <v>2.905999898910522</v>
+      </c>
+      <c r="D166" t="n">
+        <v>2.676000118255615</v>
+      </c>
+      <c r="E166" t="n">
+        <v>2.73799991607666</v>
+      </c>
+      <c r="F166" t="n">
+        <v>162239</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="n">
+        <v>45897</v>
+      </c>
+      <c r="B167" t="n">
+        <v>2.944000005722046</v>
+      </c>
+      <c r="C167" t="n">
+        <v>2.999000072479248</v>
+      </c>
+      <c r="D167" t="n">
+        <v>2.849999904632568</v>
+      </c>
+      <c r="E167" t="n">
+        <v>2.874000072479248</v>
+      </c>
+      <c r="F167" t="n">
+        <v>186265</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="n">
+        <v>45898</v>
+      </c>
+      <c r="B168" t="n">
+        <v>2.996999979019165</v>
+      </c>
+      <c r="C168" t="n">
+        <v>3.023000001907349</v>
+      </c>
+      <c r="D168" t="n">
+        <v>2.921000003814697</v>
+      </c>
+      <c r="E168" t="n">
+        <v>2.984999895095825</v>
+      </c>
+      <c r="F168" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="n">
+        <v>45902</v>
+      </c>
+      <c r="B169" t="n">
+        <v>3.009000062942505</v>
+      </c>
+      <c r="C169" t="n">
+        <v>3.065000057220459</v>
+      </c>
+      <c r="D169" t="n">
+        <v>2.86899995803833</v>
+      </c>
+      <c r="E169" t="n">
+        <v>2.971999883651733</v>
+      </c>
+      <c r="F169" t="n">
+        <v>226571</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="n">
+        <v>45903</v>
+      </c>
+      <c r="B170" t="n">
+        <v>3.063999891281128</v>
+      </c>
+      <c r="C170" t="n">
+        <v>3.13100004196167</v>
+      </c>
+      <c r="D170" t="n">
+        <v>2.96399998664856</v>
+      </c>
+      <c r="E170" t="n">
+        <v>2.992000102996826</v>
+      </c>
+      <c r="F170" t="n">
+        <v>187561</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="n">
+        <v>45904</v>
+      </c>
+      <c r="B171" t="n">
+        <v>3.073999881744385</v>
+      </c>
+      <c r="C171" t="n">
+        <v>3.130000114440918</v>
+      </c>
+      <c r="D171" t="n">
+        <v>3.022000074386597</v>
+      </c>
+      <c r="E171" t="n">
+        <v>3.075000047683716</v>
+      </c>
+      <c r="F171" t="n">
+        <v>165913</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="n">
+        <v>45905</v>
+      </c>
+      <c r="B172" t="n">
+        <v>3.04800009727478</v>
+      </c>
+      <c r="C172" t="n">
+        <v>3.130000114440918</v>
+      </c>
+      <c r="D172" t="n">
+        <v>3.020999908447266</v>
+      </c>
+      <c r="E172" t="n">
+        <v>3.078000068664551</v>
+      </c>
+      <c r="F172" t="n">
+        <v>130911</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="n">
+        <v>45908</v>
+      </c>
+      <c r="B173" t="n">
+        <v>3.089999914169312</v>
+      </c>
+      <c r="C173" t="n">
+        <v>3.197999954223633</v>
+      </c>
+      <c r="D173" t="n">
+        <v>3.055999994277954</v>
+      </c>
+      <c r="E173" t="n">
+        <v>3.086999893188477</v>
+      </c>
+      <c r="F173" t="n">
+        <v>200532</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="n">
+        <v>45909</v>
+      </c>
+      <c r="B174" t="n">
+        <v>3.117000102996826</v>
+      </c>
+      <c r="C174" t="n">
+        <v>3.164999961853027</v>
+      </c>
+      <c r="D174" t="n">
+        <v>3.046000003814697</v>
+      </c>
+      <c r="E174" t="n">
+        <v>3.098000049591064</v>
+      </c>
+      <c r="F174" t="n">
+        <v>181519</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="n">
+        <v>45910</v>
+      </c>
+      <c r="B175" t="n">
+        <v>3.029000043869019</v>
+      </c>
+      <c r="C175" t="n">
+        <v>3.117000102996826</v>
+      </c>
+      <c r="D175" t="n">
+        <v>3.007999897003174</v>
+      </c>
+      <c r="E175" t="n">
+        <v>3.107000112533569</v>
+      </c>
+      <c r="F175" t="n">
+        <v>171976</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="n">
+        <v>45911</v>
+      </c>
+      <c r="B176" t="n">
+        <v>2.934000015258789</v>
+      </c>
+      <c r="C176" t="n">
+        <v>3.062000036239624</v>
+      </c>
+      <c r="D176" t="n">
+        <v>2.91100001335144</v>
+      </c>
+      <c r="E176" t="n">
+        <v>3.029000043869019</v>
+      </c>
+      <c r="F176" t="n">
+        <v>199072</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="n">
+        <v>45912</v>
+      </c>
+      <c r="B177" t="n">
+        <v>2.940999984741211</v>
+      </c>
+      <c r="C177" t="n">
+        <v>3</v>
+      </c>
+      <c r="D177" t="n">
+        <v>2.897000074386597</v>
+      </c>
+      <c r="E177" t="n">
+        <v>2.917999982833862</v>
+      </c>
+      <c r="F177" t="n">
+        <v>160049</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="n">
+        <v>45915</v>
+      </c>
+      <c r="B178" t="n">
+        <v>3.042999982833862</v>
+      </c>
+      <c r="C178" t="n">
+        <v>3.049999952316284</v>
+      </c>
+      <c r="D178" t="n">
+        <v>2.915999889373779</v>
+      </c>
+      <c r="E178" t="n">
+        <v>2.950999975204468</v>
+      </c>
+      <c r="F178" t="n">
+        <v>152709</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="n">
+        <v>45916</v>
+      </c>
+      <c r="B179" t="n">
+        <v>3.102999925613403</v>
+      </c>
+      <c r="C179" t="n">
+        <v>3.138000011444092</v>
+      </c>
+      <c r="D179" t="n">
+        <v>2.86899995803833</v>
+      </c>
+      <c r="E179" t="n">
+        <v>3.045000076293945</v>
+      </c>
+      <c r="F179" t="n">
+        <v>166585</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="n">
+        <v>45917</v>
+      </c>
+      <c r="B180" t="n">
+        <v>3.099999904632568</v>
+      </c>
+      <c r="C180" t="n">
+        <v>3.167999982833862</v>
+      </c>
+      <c r="D180" t="n">
+        <v>3.068000078201294</v>
+      </c>
+      <c r="E180" t="n">
+        <v>3.117000102996826</v>
+      </c>
+      <c r="F180" t="n">
+        <v>132465</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="n">
+        <v>45918</v>
+      </c>
+      <c r="B181" t="n">
+        <v>2.938999891281128</v>
+      </c>
+      <c r="C181" t="n">
+        <v>3.107000112533569</v>
+      </c>
+      <c r="D181" t="n">
+        <v>2.924999952316284</v>
+      </c>
+      <c r="E181" t="n">
+        <v>3.075999975204468</v>
+      </c>
+      <c r="F181" t="n">
+        <v>180476</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="n">
+        <v>45919</v>
+      </c>
+      <c r="B182" t="n">
+        <v>2.888000011444092</v>
+      </c>
+      <c r="C182" t="n">
+        <v>2.948999881744385</v>
+      </c>
+      <c r="D182" t="n">
+        <v>2.857000112533569</v>
+      </c>
+      <c r="E182" t="n">
+        <v>2.938999891281128</v>
+      </c>
+      <c r="F182" t="n">
+        <v>142217</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="n">
+        <v>45922</v>
+      </c>
+      <c r="B183" t="n">
+        <v>2.805999994277954</v>
+      </c>
+      <c r="C183" t="n">
+        <v>2.944999933242798</v>
+      </c>
+      <c r="D183" t="n">
+        <v>2.803999900817871</v>
+      </c>
+      <c r="E183" t="n">
+        <v>2.908999919891357</v>
+      </c>
+      <c r="F183" t="n">
+        <v>163184</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="n">
+        <v>45923</v>
+      </c>
+      <c r="B184" t="n">
+        <v>2.852999925613403</v>
+      </c>
+      <c r="C184" t="n">
+        <v>2.869999885559082</v>
+      </c>
+      <c r="D184" t="n">
+        <v>2.772000074386597</v>
+      </c>
+      <c r="E184" t="n">
+        <v>2.805999994277954</v>
+      </c>
+      <c r="F184" t="n">
+        <v>70892</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="n">
+        <v>45924</v>
+      </c>
+      <c r="B185" t="n">
+        <v>2.858000040054321</v>
+      </c>
+      <c r="C185" t="n">
+        <v>2.914000034332275</v>
+      </c>
+      <c r="D185" t="n">
+        <v>2.815999984741211</v>
+      </c>
+      <c r="E185" t="n">
+        <v>2.86299991607666</v>
+      </c>
+      <c r="F185" t="n">
+        <v>55699</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="n">
+        <v>45925</v>
+      </c>
+      <c r="B186" t="n">
+        <v>2.904000043869019</v>
+      </c>
+      <c r="C186" t="n">
+        <v>2.967999935150146</v>
+      </c>
+      <c r="D186" t="n">
+        <v>2.848000049591064</v>
+      </c>
+      <c r="E186" t="n">
+        <v>2.878999948501587</v>
+      </c>
+      <c r="F186" t="n">
+        <v>74214</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="n">
+        <v>45926</v>
+      </c>
+      <c r="B187" t="n">
+        <v>2.835000038146973</v>
+      </c>
+      <c r="C187" t="n">
+        <v>2.944000005722046</v>
+      </c>
+      <c r="D187" t="n">
+        <v>2.788000106811523</v>
+      </c>
+      <c r="E187" t="n">
+        <v>2.911999940872192</v>
+      </c>
+      <c r="F187" t="n">
+        <v>168752</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="n">
+        <v>45929</v>
+      </c>
+      <c r="B188" t="n">
+        <v>3.266999959945679</v>
+      </c>
+      <c r="C188" t="n">
+        <v>3.299000024795532</v>
+      </c>
+      <c r="D188" t="n">
+        <v>3.132999897003174</v>
+      </c>
+      <c r="E188" t="n">
+        <v>3.148999929428101</v>
+      </c>
+      <c r="F188" t="n">
+        <v>166628</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="n">
+        <v>45930</v>
+      </c>
+      <c r="B189" t="n">
+        <v>3.302999973297119</v>
+      </c>
+      <c r="C189" t="n">
+        <v>3.351000070571899</v>
+      </c>
+      <c r="D189" t="n">
+        <v>3.244999885559082</v>
+      </c>
+      <c r="E189" t="n">
+        <v>3.279000043869019</v>
+      </c>
+      <c r="F189" t="n">
+        <v>162025</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="B190" t="n">
+        <v>3.476000070571899</v>
+      </c>
+      <c r="C190" t="n">
+        <v>3.492000102996826</v>
+      </c>
+      <c r="D190" t="n">
+        <v>3.318000078201294</v>
+      </c>
+      <c r="E190" t="n">
+        <v>3.331000089645386</v>
+      </c>
+      <c r="F190" t="n">
+        <v>240703</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="n">
+        <v>45932</v>
+      </c>
+      <c r="B191" t="n">
+        <v>3.441999912261963</v>
+      </c>
+      <c r="C191" t="n">
+        <v>3.585000038146973</v>
+      </c>
+      <c r="D191" t="n">
+        <v>3.401999950408936</v>
+      </c>
+      <c r="E191" t="n">
+        <v>3.457000017166138</v>
+      </c>
+      <c r="F191" t="n">
+        <v>259354</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="n">
+        <v>45933</v>
+      </c>
+      <c r="B192" t="n">
+        <v>3.323999881744385</v>
+      </c>
+      <c r="C192" t="n">
+        <v>3.450999975204468</v>
+      </c>
+      <c r="D192" t="n">
+        <v>3.306999921798706</v>
+      </c>
+      <c r="E192" t="n">
+        <v>3.413000106811523</v>
+      </c>
+      <c r="F192" t="n">
+        <v>217261</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="n">
+        <v>45936</v>
+      </c>
+      <c r="B193" t="n">
+        <v>3.357000112533569</v>
+      </c>
+      <c r="C193" t="n">
+        <v>3.484999895095825</v>
+      </c>
+      <c r="D193" t="n">
+        <v>3.296000003814697</v>
+      </c>
+      <c r="E193" t="n">
+        <v>3.299999952316284</v>
+      </c>
+      <c r="F193" t="n">
+        <v>165229</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="n">
+        <v>45937</v>
+      </c>
+      <c r="B194" t="n">
+        <v>3.497999906539917</v>
+      </c>
+      <c r="C194" t="n">
+        <v>3.523999929428101</v>
+      </c>
+      <c r="D194" t="n">
+        <v>3.355000019073486</v>
+      </c>
+      <c r="E194" t="n">
+        <v>3.398000001907349</v>
+      </c>
+      <c r="F194" t="n">
+        <v>230258</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="n">
+        <v>45938</v>
+      </c>
+      <c r="B195" t="n">
+        <v>3.33299994468689</v>
+      </c>
+      <c r="C195" t="n">
+        <v>3.549999952316284</v>
+      </c>
+      <c r="D195" t="n">
+        <v>3.315999984741211</v>
+      </c>
+      <c r="E195" t="n">
+        <v>3.523999929428101</v>
+      </c>
+      <c r="F195" t="n">
+        <v>242687</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="n">
+        <v>45939</v>
+      </c>
+      <c r="B196" t="n">
+        <v>3.269000053405762</v>
+      </c>
+      <c r="C196" t="n">
+        <v>3.392999887466431</v>
+      </c>
+      <c r="D196" t="n">
+        <v>3.234999895095825</v>
+      </c>
+      <c r="E196" t="n">
+        <v>3.335999965667725</v>
+      </c>
+      <c r="F196" t="n">
+        <v>198680</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="n">
+        <v>45940</v>
+      </c>
+      <c r="B197" t="n">
+        <v>3.105999946594238</v>
+      </c>
+      <c r="C197" t="n">
+        <v>3.253000020980835</v>
+      </c>
+      <c r="D197" t="n">
+        <v>3.08899998664856</v>
+      </c>
+      <c r="E197" t="n">
+        <v>3.239000082015991</v>
+      </c>
+      <c r="F197" t="n">
+        <v>195346</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="n">
+        <v>45943</v>
+      </c>
+      <c r="B198" t="n">
+        <v>3.118000030517578</v>
+      </c>
+      <c r="C198" t="n">
+        <v>3.138000011444092</v>
+      </c>
+      <c r="D198" t="n">
+        <v>3.029000043869019</v>
+      </c>
+      <c r="E198" t="n">
+        <v>3.099999904632568</v>
+      </c>
+      <c r="F198" t="n">
+        <v>195346</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="n">
+        <v>45944</v>
+      </c>
+      <c r="B199" t="n">
+        <v>3.028000116348267</v>
+      </c>
+      <c r="C199" t="n">
+        <v>3.105999946594238</v>
+      </c>
+      <c r="D199" t="n">
+        <v>3.003999948501587</v>
+      </c>
+      <c r="E199" t="n">
+        <v>3.102999925613403</v>
+      </c>
+      <c r="F199" t="n">
+        <v>150478</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="n">
+        <v>45945</v>
+      </c>
+      <c r="B200" t="n">
+        <v>3.016000032424927</v>
+      </c>
+      <c r="C200" t="n">
+        <v>3.040999889373779</v>
+      </c>
+      <c r="D200" t="n">
+        <v>2.96399998664856</v>
+      </c>
+      <c r="E200" t="n">
+        <v>3.029000043869019</v>
+      </c>
+      <c r="F200" t="n">
+        <v>149150</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="n">
+        <v>45946</v>
+      </c>
+      <c r="B201" t="n">
+        <v>2.937999963760376</v>
+      </c>
+      <c r="C201" t="n">
+        <v>3.066999912261963</v>
+      </c>
+      <c r="D201" t="n">
+        <v>2.921999931335449</v>
+      </c>
+      <c r="E201" t="n">
+        <v>3.03600001335144</v>
+      </c>
+      <c r="F201" t="n">
+        <v>161360</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="n">
+        <v>45947</v>
+      </c>
+      <c r="B202" t="n">
+        <v>3.007999897003174</v>
+      </c>
+      <c r="C202" t="n">
+        <v>3.023999929428101</v>
+      </c>
+      <c r="D202" t="n">
+        <v>2.892999887466431</v>
+      </c>
+      <c r="E202" t="n">
+        <v>2.926000118255615</v>
+      </c>
+      <c r="F202" t="n">
+        <v>128236</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="n">
+        <v>45950</v>
+      </c>
+      <c r="B203" t="n">
+        <v>3.397000074386597</v>
+      </c>
+      <c r="C203" t="n">
+        <v>3.430000066757202</v>
+      </c>
+      <c r="D203" t="n">
+        <v>3.135999917984009</v>
+      </c>
+      <c r="E203" t="n">
+        <v>3.160000085830688</v>
+      </c>
+      <c r="F203" t="n">
+        <v>266597</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="n">
+        <v>45951</v>
+      </c>
+      <c r="B204" t="n">
+        <v>3.473999977111816</v>
+      </c>
+      <c r="C204" t="n">
+        <v>3.503999948501587</v>
+      </c>
+      <c r="D204" t="n">
+        <v>3.357000112533569</v>
+      </c>
+      <c r="E204" t="n">
+        <v>3.421000003814697</v>
+      </c>
+      <c r="F204" t="n">
+        <v>197775</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="n">
+        <v>45952</v>
+      </c>
+      <c r="B205" t="n">
+        <v>3.450000047683716</v>
+      </c>
+      <c r="C205" t="n">
+        <v>3.572000026702881</v>
+      </c>
+      <c r="D205" t="n">
+        <v>3.385999917984009</v>
+      </c>
+      <c r="E205" t="n">
+        <v>3.486999988555908</v>
+      </c>
+      <c r="F205" t="n">
+        <v>202361</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="n">
+        <v>45953</v>
+      </c>
+      <c r="B206" t="n">
+        <v>3.344000101089478</v>
+      </c>
+      <c r="C206" t="n">
+        <v>3.506999969482422</v>
+      </c>
+      <c r="D206" t="n">
+        <v>3.289999961853027</v>
+      </c>
+      <c r="E206" t="n">
+        <v>3.438999891281128</v>
+      </c>
+      <c r="F206" t="n">
+        <v>157089</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="n">
+        <v>45954</v>
+      </c>
+      <c r="B207" t="n">
+        <v>3.303999900817871</v>
+      </c>
+      <c r="C207" t="n">
+        <v>3.397000074386597</v>
+      </c>
+      <c r="D207" t="n">
+        <v>3.200000047683716</v>
+      </c>
+      <c r="E207" t="n">
+        <v>3.285000085830688</v>
+      </c>
+      <c r="F207" t="n">
+        <v>108141</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="n">
+        <v>45957</v>
+      </c>
+      <c r="B208" t="n">
+        <v>3.441999912261963</v>
+      </c>
+      <c r="C208" t="n">
+        <v>3.469000101089478</v>
+      </c>
+      <c r="D208" t="n">
+        <v>3.260999917984009</v>
+      </c>
+      <c r="E208" t="n">
+        <v>3.410000085830688</v>
+      </c>
+      <c r="F208" t="n">
+        <v>67444</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="n">
+        <v>45958</v>
+      </c>
+      <c r="B209" t="n">
+        <v>3.345000028610229</v>
+      </c>
+      <c r="C209" t="n">
+        <v>3.434999942779541</v>
+      </c>
+      <c r="D209" t="n">
+        <v>3.239000082015991</v>
+      </c>
+      <c r="E209" t="n">
+        <v>3.41100001335144</v>
+      </c>
+      <c r="F209" t="n">
+        <v>85022</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="n">
+        <v>45959</v>
+      </c>
+      <c r="B210" t="n">
+        <v>3.375999927520752</v>
+      </c>
+      <c r="C210" t="n">
+        <v>3.404999971389771</v>
+      </c>
+      <c r="D210" t="n">
+        <v>3.193000078201294</v>
+      </c>
+      <c r="E210" t="n">
+        <v>3.270999908447266</v>
+      </c>
+      <c r="F210" t="n">
+        <v>153684</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="n">
+        <v>45960</v>
+      </c>
+      <c r="B211" t="n">
+        <v>3.956000089645386</v>
+      </c>
+      <c r="C211" t="n">
+        <v>4.071000099182129</v>
+      </c>
+      <c r="D211" t="n">
+        <v>3.78600001335144</v>
+      </c>
+      <c r="E211" t="n">
+        <v>3.79800009727478</v>
+      </c>
+      <c r="F211" t="n">
+        <v>201075</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="n">
+        <v>45961</v>
+      </c>
+      <c r="B212" t="n">
+        <v>4.124000072479248</v>
+      </c>
+      <c r="C212" t="n">
+        <v>4.157000064849854</v>
+      </c>
+      <c r="D212" t="n">
+        <v>4.014999866485596</v>
+      </c>
+      <c r="E212" t="n">
+        <v>4.060999870300293</v>
+      </c>
+      <c r="F212" t="n">
+        <v>238492</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="n">
+        <v>45964</v>
+      </c>
+      <c r="B213" t="n">
+        <v>4.265999794006348</v>
+      </c>
+      <c r="C213" t="n">
+        <v>4.297999858856201</v>
+      </c>
+      <c r="D213" t="n">
+        <v>4.086999893188477</v>
+      </c>
+      <c r="E213" t="n">
+        <v>4.159999847412109</v>
+      </c>
+      <c r="F213" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="B214" t="n">
+        <v>4.342999935150146</v>
+      </c>
+      <c r="C214" t="n">
+        <v>4.395999908447266</v>
+      </c>
+      <c r="D214" t="n">
+        <v>4.183000087738037</v>
+      </c>
+      <c r="E214" t="n">
+        <v>4.25600004196167</v>
+      </c>
+      <c r="F214" t="n">
+        <v>231288</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="B215" t="n">
+        <v>4.23199987411499</v>
+      </c>
+      <c r="C215" t="n">
+        <v>4.35099983215332</v>
+      </c>
+      <c r="D215" t="n">
+        <v>4.205999851226807</v>
+      </c>
+      <c r="E215" t="n">
+        <v>4.320000171661377</v>
+      </c>
+      <c r="F215" t="n">
+        <v>156270</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B216" t="n">
+        <v>4.35699987411499</v>
+      </c>
+      <c r="C216" t="n">
+        <v>4.420000076293945</v>
+      </c>
+      <c r="D216" t="n">
+        <v>4.191999912261963</v>
+      </c>
+      <c r="E216" t="n">
+        <v>4.238999843597412</v>
+      </c>
+      <c r="F216" t="n">
+        <v>193866</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="n">
+        <v>45968</v>
+      </c>
+      <c r="B217" t="n">
+        <v>4.315000057220459</v>
+      </c>
+      <c r="C217" t="n">
+        <v>4.419000148773193</v>
+      </c>
+      <c r="D217" t="n">
+        <v>4.26800012588501</v>
+      </c>
+      <c r="E217" t="n">
+        <v>4.413000106811523</v>
+      </c>
+      <c r="F217" t="n">
+        <v>178319</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="n">
+        <v>45971</v>
+      </c>
+      <c r="B218" t="n">
+        <v>4.337999820709229</v>
+      </c>
+      <c r="C218" t="n">
+        <v>4.508999824523926</v>
+      </c>
+      <c r="D218" t="n">
+        <v>4.26200008392334</v>
+      </c>
+      <c r="E218" t="n">
+        <v>4.480000019073486</v>
+      </c>
+      <c r="F218" t="n">
+        <v>189080</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="n">
+        <v>45972</v>
+      </c>
+      <c r="B219" t="n">
+        <v>4.565000057220459</v>
+      </c>
+      <c r="C219" t="n">
+        <v>4.580999851226807</v>
+      </c>
+      <c r="D219" t="n">
+        <v>4.276000022888184</v>
+      </c>
+      <c r="E219" t="n">
+        <v>4.375</v>
+      </c>
+      <c r="F219" t="n">
+        <v>243691</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="n">
+        <v>45973</v>
+      </c>
+      <c r="B220" t="n">
+        <v>4.532999992370605</v>
+      </c>
+      <c r="C220" t="n">
+        <v>4.581999778747559</v>
+      </c>
+      <c r="D220" t="n">
+        <v>4.460999965667725</v>
+      </c>
+      <c r="E220" t="n">
+        <v>4.526000022888184</v>
+      </c>
+      <c r="F220" t="n">
+        <v>170351</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="n">
+        <v>45974</v>
+      </c>
+      <c r="B221" t="n">
+        <v>4.645999908447266</v>
+      </c>
+      <c r="C221" t="n">
+        <v>4.688000202178955</v>
+      </c>
+      <c r="D221" t="n">
+        <v>4.453999996185303</v>
+      </c>
+      <c r="E221" t="n">
+        <v>4.534999847412109</v>
+      </c>
+      <c r="F221" t="n">
+        <v>201019</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="n">
+        <v>45975</v>
+      </c>
+      <c r="B222" t="n">
+        <v>4.565999984741211</v>
+      </c>
+      <c r="C222" t="n">
+        <v>4.635000228881836</v>
+      </c>
+      <c r="D222" t="n">
+        <v>4.375999927520752</v>
+      </c>
+      <c r="E222" t="n">
+        <v>4.597000122070312</v>
+      </c>
+      <c r="F222" t="n">
+        <v>227908</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="n">
+        <v>45978</v>
+      </c>
+      <c r="B223" t="n">
+        <v>4.361000061035156</v>
+      </c>
+      <c r="C223" t="n">
+        <v>4.540999889373779</v>
+      </c>
+      <c r="D223" t="n">
+        <v>4.322999954223633</v>
+      </c>
+      <c r="E223" t="n">
+        <v>4.531000137329102</v>
+      </c>
+      <c r="F223" t="n">
+        <v>191623</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="n">
+        <v>45979</v>
+      </c>
+      <c r="B224" t="n">
+        <v>4.370999813079834</v>
+      </c>
+      <c r="C224" t="n">
+        <v>4.401000022888184</v>
+      </c>
+      <c r="D224" t="n">
+        <v>4.235000133514404</v>
+      </c>
+      <c r="E224" t="n">
+        <v>4.342000007629395</v>
+      </c>
+      <c r="F224" t="n">
+        <v>204812</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="n">
+        <v>45980</v>
+      </c>
+      <c r="B225" t="n">
+        <v>4.550000190734863</v>
+      </c>
+      <c r="C225" t="n">
+        <v>4.60200023651123</v>
+      </c>
+      <c r="D225" t="n">
+        <v>4.349999904632568</v>
+      </c>
+      <c r="E225" t="n">
+        <v>4.374000072479248</v>
+      </c>
+      <c r="F225" t="n">
+        <v>152272</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="n">
+        <v>45981</v>
+      </c>
+      <c r="B226" t="n">
+        <v>4.473999977111816</v>
+      </c>
+      <c r="C226" t="n">
+        <v>4.611999988555908</v>
+      </c>
+      <c r="D226" t="n">
+        <v>4.458000183105469</v>
+      </c>
+      <c r="E226" t="n">
+        <v>4.565999984741211</v>
+      </c>
+      <c r="F226" t="n">
+        <v>105538</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="n">
+        <v>45982</v>
+      </c>
+      <c r="B227" t="n">
+        <v>4.579999923706055</v>
+      </c>
+      <c r="C227" t="n">
+        <v>4.675000190734863</v>
+      </c>
+      <c r="D227" t="n">
+        <v>4.460999965667725</v>
+      </c>
+      <c r="E227" t="n">
+        <v>4.488999843597412</v>
+      </c>
+      <c r="F227" t="n">
+        <v>80707</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="n">
+        <v>45985</v>
+      </c>
+      <c r="B228" t="n">
+        <v>4.548999786376953</v>
+      </c>
+      <c r="C228" t="n">
+        <v>4.576000213623047</v>
+      </c>
+      <c r="D228" t="n">
+        <v>4.443999767303467</v>
+      </c>
+      <c r="E228" t="n">
+        <v>4.465000152587891</v>
+      </c>
+      <c r="F228" t="n">
+        <v>78483</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="n">
+        <v>45986</v>
+      </c>
+      <c r="B229" t="n">
+        <v>4.423999786376953</v>
+      </c>
+      <c r="C229" t="n">
+        <v>4.546999931335449</v>
+      </c>
+      <c r="D229" t="n">
+        <v>4.267000198364258</v>
+      </c>
+      <c r="E229" t="n">
+        <v>4.500999927520752</v>
+      </c>
+      <c r="F229" t="n">
+        <v>240457</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="n">
+        <v>45987</v>
+      </c>
+      <c r="B230" t="n">
+        <v>4.558000087738037</v>
+      </c>
+      <c r="C230" t="n">
+        <v>4.644000053405762</v>
+      </c>
+      <c r="D230" t="n">
+        <v>4.441999912261963</v>
+      </c>
+      <c r="E230" t="n">
+        <v>4.482999801635742</v>
+      </c>
+      <c r="F230" t="n">
+        <v>155159</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="n">
+        <v>45989</v>
+      </c>
+      <c r="B231" t="n">
+        <v>4.849999904632568</v>
+      </c>
+      <c r="C231" t="n">
+        <v>4.870999813079834</v>
+      </c>
+      <c r="D231" t="n">
+        <v>4.526999950408936</v>
+      </c>
+      <c r="E231" t="n">
+        <v>4.618000030517578</v>
+      </c>
+      <c r="F231" t="n">
+        <v>127694</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B232" t="n">
+        <v>4.921000003814697</v>
+      </c>
+      <c r="C232" t="n">
+        <v>4.952000141143799</v>
+      </c>
+      <c r="D232" t="n">
+        <v>4.757999897003174</v>
+      </c>
+      <c r="E232" t="n">
+        <v>4.869999885559082</v>
+      </c>
+      <c r="F232" t="n">
+        <v>209469</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="n">
+        <v>45993</v>
+      </c>
+      <c r="B233" t="n">
+        <v>4.840000152587891</v>
+      </c>
+      <c r="C233" t="n">
+        <v>4.984000205993652</v>
+      </c>
+      <c r="D233" t="n">
+        <v>4.804999828338623</v>
+      </c>
+      <c r="E233" t="n">
+        <v>4.901999950408936</v>
+      </c>
+      <c r="F233" t="n">
+        <v>172375</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="n">
+        <v>45994</v>
+      </c>
+      <c r="B234" t="n">
+        <v>4.994999885559082</v>
+      </c>
+      <c r="C234" t="n">
+        <v>5.039000034332275</v>
+      </c>
+      <c r="D234" t="n">
+        <v>4.818999767303467</v>
+      </c>
+      <c r="E234" t="n">
+        <v>4.827000141143799</v>
+      </c>
+      <c r="F234" t="n">
+        <v>186366</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="n">
+        <v>45995</v>
+      </c>
+      <c r="B235" t="n">
+        <v>5.063000202178955</v>
+      </c>
+      <c r="C235" t="n">
+        <v>5.090000152587891</v>
+      </c>
+      <c r="D235" t="n">
+        <v>4.870999813079834</v>
+      </c>
+      <c r="E235" t="n">
+        <v>5.010000228881836</v>
+      </c>
+      <c r="F235" t="n">
+        <v>209843</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="B236" t="n">
+        <v>5.289000034332275</v>
+      </c>
+      <c r="C236" t="n">
+        <v>5.495999813079834</v>
+      </c>
+      <c r="D236" t="n">
+        <v>5.026999950408936</v>
+      </c>
+      <c r="E236" t="n">
+        <v>5.077000141143799</v>
+      </c>
+      <c r="F236" t="n">
+        <v>376679</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="n">
+        <v>45999</v>
+      </c>
+      <c r="B237" t="n">
+        <v>4.912000179290771</v>
+      </c>
+      <c r="C237" t="n">
+        <v>5.204999923706055</v>
+      </c>
+      <c r="D237" t="n">
+        <v>4.849999904632568</v>
+      </c>
+      <c r="E237" t="n">
+        <v>5.099999904632568</v>
+      </c>
+      <c r="F237" t="n">
+        <v>301953</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="n">
+        <v>46000</v>
+      </c>
+      <c r="B238" t="n">
+        <v>4.573999881744385</v>
+      </c>
+      <c r="C238" t="n">
+        <v>4.877999782562256</v>
+      </c>
+      <c r="D238" t="n">
+        <v>4.551000118255615</v>
+      </c>
+      <c r="E238" t="n">
+        <v>4.868000030517578</v>
+      </c>
+      <c r="F238" t="n">
+        <v>249501</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="n">
+        <v>46001</v>
+      </c>
+      <c r="B239" t="n">
+        <v>4.59499979019165</v>
+      </c>
+      <c r="C239" t="n">
+        <v>4.696000099182129</v>
+      </c>
+      <c r="D239" t="n">
+        <v>4.454999923706055</v>
+      </c>
+      <c r="E239" t="n">
+        <v>4.578000068664551</v>
+      </c>
+      <c r="F239" t="n">
+        <v>271105</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="n">
+        <v>46002</v>
+      </c>
+      <c r="B240" t="n">
+        <v>4.230999946594238</v>
+      </c>
+      <c r="C240" t="n">
+        <v>4.63100004196167</v>
+      </c>
+      <c r="D240" t="n">
+        <v>4.196000099182129</v>
+      </c>
+      <c r="E240" t="n">
+        <v>4.625999927520752</v>
+      </c>
+      <c r="F240" t="n">
+        <v>287859</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="n">
+        <v>46003</v>
+      </c>
+      <c r="B241" t="n">
+        <v>4.11299991607666</v>
+      </c>
+      <c r="C241" t="n">
+        <v>4.256999969482422</v>
+      </c>
+      <c r="D241" t="n">
+        <v>4.065000057220459</v>
+      </c>
+      <c r="E241" t="n">
+        <v>4.230999946594238</v>
+      </c>
+      <c r="F241" t="n">
+        <v>199844</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B242" t="n">
+        <v>4.01200008392334</v>
+      </c>
+      <c r="C242" t="n">
+        <v>4.217999935150146</v>
+      </c>
+      <c r="D242" t="n">
+        <v>3.993000030517578</v>
+      </c>
+      <c r="E242" t="n">
+        <v>4.171000003814697</v>
+      </c>
+      <c r="F242" t="n">
+        <v>169239</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="n">
+        <v>46007</v>
+      </c>
+      <c r="B243" t="n">
+        <v>3.885999917984009</v>
+      </c>
+      <c r="C243" t="n">
+        <v>4.045000076293945</v>
+      </c>
+      <c r="D243" t="n">
+        <v>3.842000007629395</v>
+      </c>
+      <c r="E243" t="n">
+        <v>4.037000179290771</v>
+      </c>
+      <c r="F243" t="n">
+        <v>155859</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="n">
+        <v>46008</v>
+      </c>
+      <c r="B244" t="n">
+        <v>4.02400016784668</v>
+      </c>
+      <c r="C244" t="n">
+        <v>4.113999843597412</v>
+      </c>
+      <c r="D244" t="n">
+        <v>3.920000076293945</v>
+      </c>
+      <c r="E244" t="n">
+        <v>3.936000108718872</v>
+      </c>
+      <c r="F244" t="n">
+        <v>153559</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B245" t="n">
+        <v>3.907999992370605</v>
+      </c>
+      <c r="C245" t="n">
+        <v>4.217999935150146</v>
+      </c>
+      <c r="D245" t="n">
+        <v>3.877000093460083</v>
+      </c>
+      <c r="E245" t="n">
+        <v>4.117000102996826</v>
+      </c>
+      <c r="F245" t="n">
+        <v>158058</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="n">
+        <v>46010</v>
+      </c>
+      <c r="B246" t="n">
+        <v>3.983999967575073</v>
+      </c>
+      <c r="C246" t="n">
+        <v>4.03000020980835</v>
+      </c>
+      <c r="D246" t="n">
+        <v>3.839999914169312</v>
+      </c>
+      <c r="E246" t="n">
+        <v>3.941999912261963</v>
+      </c>
+      <c r="F246" t="n">
+        <v>145508</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="n">
+        <v>46013</v>
+      </c>
+      <c r="B247" t="n">
+        <v>3.964999914169312</v>
+      </c>
+      <c r="C247" t="n">
+        <v>4.139999866485596</v>
+      </c>
+      <c r="D247" t="n">
+        <v>3.796999931335449</v>
+      </c>
+      <c r="E247" t="n">
+        <v>4.080999851226807</v>
+      </c>
+      <c r="F247" t="n">
+        <v>157602</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="n">
+        <v>46014</v>
+      </c>
+      <c r="B248" t="n">
+        <v>4.407999992370605</v>
+      </c>
+      <c r="C248" t="n">
+        <v>4.448999881744385</v>
+      </c>
+      <c r="D248" t="n">
+        <v>3.943000078201294</v>
+      </c>
+      <c r="E248" t="n">
+        <v>3.990000009536743</v>
+      </c>
+      <c r="F248" t="n">
+        <v>126794</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="n">
+        <v>46015</v>
+      </c>
+      <c r="B249" t="n">
+        <v>4.242000102996826</v>
+      </c>
+      <c r="C249" t="n">
+        <v>4.592999935150146</v>
+      </c>
+      <c r="D249" t="n">
+        <v>4.179999828338623</v>
+      </c>
+      <c r="E249" t="n">
+        <v>4.414999961853027</v>
+      </c>
+      <c r="F249" t="n">
+        <v>57070</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="n">
+        <v>46017</v>
+      </c>
+      <c r="B250" t="n">
+        <v>4.366000175476074</v>
+      </c>
+      <c r="C250" t="n">
+        <v>4.421000003814697</v>
+      </c>
+      <c r="D250" t="n">
+        <v>4.196000099182129</v>
+      </c>
+      <c r="E250" t="n">
+        <v>4.196000099182129</v>
+      </c>
+      <c r="F250" t="n">
+        <v>46351</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="n">
+        <v>46020</v>
+      </c>
+      <c r="B251" t="n">
+        <v>4.686999797821045</v>
+      </c>
+      <c r="C251" t="n">
+        <v>4.721000194549561</v>
+      </c>
+      <c r="D251" t="n">
+        <v>4.35099983215332</v>
+      </c>
+      <c r="E251" t="n">
+        <v>4.449999809265137</v>
+      </c>
+      <c r="F251" t="n">
+        <v>163457</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="B252" t="n">
+        <v>3.971999883651733</v>
+      </c>
+      <c r="C252" t="n">
+        <v>4.176000118255615</v>
+      </c>
+      <c r="D252" t="n">
+        <v>3.915999889373779</v>
+      </c>
+      <c r="E252" t="n">
+        <v>3.947000026702881</v>
+      </c>
+      <c r="F252" t="n">
+        <v>136981</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B253" t="n">
+        <v>3.686000108718872</v>
+      </c>
+      <c r="C253" t="n">
+        <v>3.983000040054321</v>
+      </c>
+      <c r="D253" t="n">
+        <v>3.678999900817871</v>
+      </c>
+      <c r="E253" t="n">
+        <v>3.976000070571899</v>
+      </c>
+      <c r="F253" t="n">
+        <v>132231</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="n">
+        <v>46024</v>
+      </c>
+      <c r="B254" t="n">
+        <v>3.618000030517578</v>
+      </c>
+      <c r="C254" t="n">
+        <v>3.703000068664551</v>
+      </c>
+      <c r="D254" t="n">
+        <v>3.562999963760376</v>
+      </c>
+      <c r="E254" t="n">
+        <v>3.678999900817871</v>
+      </c>
+      <c r="F254" t="n">
+        <v>133024</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="n">
+        <v>46027</v>
+      </c>
+      <c r="B255" t="n">
+        <v>3.523000001907349</v>
+      </c>
+      <c r="C255" t="n">
+        <v>3.529999971389771</v>
+      </c>
+      <c r="D255" t="n">
+        <v>3.355000019073486</v>
+      </c>
+      <c r="E255" t="n">
+        <v>3.506999969482422</v>
+      </c>
+      <c r="F255" t="n">
+        <v>228737</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="n">
+        <v>46028</v>
+      </c>
+      <c r="B256" t="n">
+        <v>3.349999904632568</v>
+      </c>
+      <c r="C256" t="n">
+        <v>3.502000093460083</v>
+      </c>
+      <c r="D256" t="n">
+        <v>3.323999881744385</v>
+      </c>
+      <c r="E256" t="n">
+        <v>3.492000102996826</v>
+      </c>
+      <c r="F256" t="n">
+        <v>145165</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="n">
+        <v>46029</v>
+      </c>
+      <c r="B257" t="n">
+        <v>3.525000095367432</v>
+      </c>
+      <c r="C257" t="n">
+        <v>3.591000080108643</v>
+      </c>
+      <c r="D257" t="n">
+        <v>3.418999910354614</v>
+      </c>
+      <c r="E257" t="n">
+        <v>3.424999952316284</v>
+      </c>
+      <c r="F257" t="n">
+        <v>151941</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="n">
+        <v>46030</v>
+      </c>
+      <c r="B258" t="n">
+        <v>3.407000064849854</v>
+      </c>
+      <c r="C258" t="n">
+        <v>3.634000062942505</v>
+      </c>
+      <c r="D258" t="n">
+        <v>3.355000019073486</v>
+      </c>
+      <c r="E258" t="n">
+        <v>3.562999963760376</v>
+      </c>
+      <c r="F258" t="n">
+        <v>193218</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="n">
+        <v>46031</v>
+      </c>
+      <c r="B259" t="n">
+        <v>3.168999910354614</v>
+      </c>
+      <c r="C259" t="n">
+        <v>3.496000051498413</v>
+      </c>
+      <c r="D259" t="n">
+        <v>3.13100004196167</v>
+      </c>
+      <c r="E259" t="n">
+        <v>3.410000085830688</v>
+      </c>
+      <c r="F259" t="n">
+        <v>322218</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="n">
+        <v>46034</v>
+      </c>
+      <c r="B260" t="n">
+        <v>3.408999919891357</v>
+      </c>
+      <c r="C260" t="n">
+        <v>3.430999994277954</v>
+      </c>
+      <c r="D260" t="n">
+        <v>3.181999921798706</v>
+      </c>
+      <c r="E260" t="n">
+        <v>3.289999961853027</v>
+      </c>
+      <c r="F260" t="n">
+        <v>248893</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="n">
+        <v>46035</v>
+      </c>
+      <c r="B261" t="n">
+        <v>3.418999910354614</v>
+      </c>
+      <c r="C261" t="n">
+        <v>3.499000072479248</v>
+      </c>
+      <c r="D261" t="n">
+        <v>3.29800009727478</v>
+      </c>
+      <c r="E261" t="n">
+        <v>3.358000040054321</v>
+      </c>
+      <c r="F261" t="n">
+        <v>187132</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="n">
+        <v>46036</v>
+      </c>
+      <c r="B262" t="n">
+        <v>3.119999885559082</v>
+      </c>
+      <c r="C262" t="n">
+        <v>3.443000078201294</v>
+      </c>
+      <c r="D262" t="n">
+        <v>3.068000078201294</v>
+      </c>
+      <c r="E262" t="n">
+        <v>3.384000062942505</v>
+      </c>
+      <c r="F262" t="n">
+        <v>215332</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="n">
+        <v>46037</v>
+      </c>
+      <c r="B263" t="n">
+        <v>3.128000020980835</v>
+      </c>
+      <c r="C263" t="n">
+        <v>3.217999935150146</v>
+      </c>
+      <c r="D263" t="n">
+        <v>3.00600004196167</v>
+      </c>
+      <c r="E263" t="n">
+        <v>3.101999998092651</v>
+      </c>
+      <c r="F263" t="n">
+        <v>180723</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="n">
+        <v>46038</v>
+      </c>
+      <c r="B264" t="n">
+        <v>3.102999925613403</v>
+      </c>
+      <c r="C264" t="n">
+        <v>3.230000019073486</v>
+      </c>
+      <c r="D264" t="n">
+        <v>3.019999980926514</v>
+      </c>
+      <c r="E264" t="n">
+        <v>3.145999908447266</v>
+      </c>
+      <c r="F264" t="n">
+        <v>139667</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="n">
+        <v>46042</v>
+      </c>
+      <c r="B265" t="n">
+        <v>3.907000064849854</v>
+      </c>
+      <c r="C265" t="n">
+        <v>3.990000009536743</v>
+      </c>
+      <c r="D265" t="n">
+        <v>3.380000114440918</v>
+      </c>
+      <c r="E265" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F265" t="n">
+        <v>410520</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="n">
+        <v>46043</v>
+      </c>
+      <c r="B266" t="n">
+        <v>4.875</v>
+      </c>
+      <c r="C266" t="n">
+        <v>5.098999977111816</v>
+      </c>
+      <c r="D266" t="n">
+        <v>3.834000110626221</v>
+      </c>
+      <c r="E266" t="n">
+        <v>3.903000116348267</v>
+      </c>
+      <c r="F266" t="n">
+        <v>367003</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="n">
+        <v>46044</v>
+      </c>
+      <c r="B267" t="n">
+        <v>5.045000076293945</v>
+      </c>
+      <c r="C267" t="n">
+        <v>5.650000095367432</v>
+      </c>
+      <c r="D267" t="n">
+        <v>4.769000053405762</v>
+      </c>
+      <c r="E267" t="n">
+        <v>5.039000034332275</v>
+      </c>
+      <c r="F267" t="n">
+        <v>310947</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="n">
+        <v>46045</v>
+      </c>
+      <c r="B268" t="n">
+        <v>5.275000095367432</v>
+      </c>
+      <c r="C268" t="n">
+        <v>5.434000015258789</v>
+      </c>
+      <c r="D268" t="n">
+        <v>4.659999847412109</v>
+      </c>
+      <c r="E268" t="n">
+        <v>4.872000217437744</v>
+      </c>
+      <c r="F268" t="n">
+        <v>107108</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="n">
+        <v>46048</v>
+      </c>
+      <c r="B269" t="n">
+        <v>6.800000190734863</v>
+      </c>
+      <c r="C269" t="n">
+        <v>7.439000129699707</v>
+      </c>
+      <c r="D269" t="n">
+        <v>5.728000164031982</v>
+      </c>
+      <c r="E269" t="n">
+        <v>5.790999889373779</v>
+      </c>
+      <c r="F269" t="n">
+        <v>99498</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="n">
+        <v>46049</v>
+      </c>
+      <c r="B270" t="n">
+        <v>6.953999996185303</v>
+      </c>
+      <c r="C270" t="n">
+        <v>7.309999942779541</v>
+      </c>
+      <c r="D270" t="n">
+        <v>5.771999835968018</v>
+      </c>
+      <c r="E270" t="n">
+        <v>6.645999908447266</v>
+      </c>
+      <c r="F270" t="n">
+        <v>77676</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="2" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B271" t="n">
+        <v>7.460000038146973</v>
+      </c>
+      <c r="C271" t="n">
+        <v>7.827000141143799</v>
+      </c>
+      <c r="D271" t="n">
+        <v>5.900000095367432</v>
+      </c>
+      <c r="E271" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F271" t="n">
+        <v>235065</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="2" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B272" t="n">
+        <v>3.917999982833862</v>
+      </c>
+      <c r="C272" t="n">
+        <v>3.930000066757202</v>
+      </c>
+      <c r="D272" t="n">
+        <v>3.727999925613403</v>
+      </c>
+      <c r="E272" t="n">
+        <v>3.742000102996826</v>
+      </c>
+      <c r="F272" t="n">
+        <v>234642</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="n">
         <v>46052</v>
       </c>
-      <c r="B21" t="n">
+      <c r="B273" t="n">
         <v>4.354000091552734</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C273" t="n">
         <v>4.425000190734863</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D273" t="n">
         <v>3.818000078201294</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E273" t="n">
         <v>3.878999948501587</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F273" t="n">
         <v>234642</v>
       </c>
     </row>
